--- a/outputs/daily/hr_rankings_2026-08-03_full.xlsx
+++ b/outputs/daily/hr_rankings_2026-08-03_full.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BJ136"/>
+  <dimension ref="A1:BJ135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27039,12 +27039,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>686668</t>
+          <t>678662</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Brenton Doyle</t>
+          <t>Ezequiel Tovar</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -27088,7 +27088,7 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>38.2</v>
+        <v>38.4</v>
       </c>
       <c r="M99" t="inlineStr">
         <is>
@@ -27106,7 +27106,7 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>23.7</v>
+        <v>27.9</v>
       </c>
       <c r="Q99" t="n">
         <v>39.2</v>
@@ -27121,7 +27121,7 @@
         <v>78</v>
       </c>
       <c r="U99" t="n">
-        <v>29.4</v>
+        <v>5.7</v>
       </c>
       <c r="V99" t="inlineStr">
         <is>
@@ -27177,7 +27177,7 @@
       </c>
       <c r="AH99" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI99" t="inlineStr">
@@ -27192,7 +27192,7 @@
       </c>
       <c r="AK99" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/19, 0 HR</t>
+          <t>Last 7 games: 3/19, 0 HR</t>
         </is>
       </c>
       <c r="AL99" t="inlineStr">
@@ -27207,67 +27207,67 @@
       </c>
       <c r="AN99" t="inlineStr">
         <is>
-          <t>7.19</t>
+          <t>7.13</t>
         </is>
       </c>
       <c r="AO99" t="inlineStr">
         <is>
-          <t>38.58</t>
+          <t>34.98</t>
         </is>
       </c>
       <c r="AP99" t="inlineStr">
         <is>
-          <t>88.64</t>
+          <t>87.86</t>
         </is>
       </c>
       <c r="AQ99" t="inlineStr">
         <is>
-          <t>99.7114</t>
+          <t>98.8607</t>
         </is>
       </c>
       <c r="AR99" t="inlineStr">
         <is>
-          <t>0.3134</t>
+          <t>0.3759</t>
         </is>
       </c>
       <c r="AS99" t="inlineStr">
         <is>
-          <t>0.1067</t>
+          <t>0.1499</t>
         </is>
       </c>
       <c r="AT99" t="inlineStr">
         <is>
-          <t>0.2624</t>
+          <t>0.2812</t>
         </is>
       </c>
       <c r="AU99" t="inlineStr">
         <is>
-          <t>71.61</t>
+          <t>71.95</t>
         </is>
       </c>
       <c r="AV99" t="inlineStr">
         <is>
-          <t>13.62</t>
+          <t>20.82</t>
         </is>
       </c>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>40.91</t>
+          <t>37.19</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>21.77</t>
+          <t>29.64</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>0.0905</t>
+          <t>0.1288</t>
         </is>
       </c>
       <c r="BA99" t="inlineStr">
@@ -28419,27 +28419,27 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>678662</t>
+          <t>592663</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Ezequiel Tovar</t>
+          <t>J.T. Realmuto</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-08-04T00:40:00Z</t>
+          <t>2026-08-03T22:40:00Z</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -28449,17 +28449,17 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>Ian Seymour</t>
+          <t>Andrew Alvarez</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>693855</t>
+          <t>674841</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
@@ -28468,7 +28468,7 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>37.4</v>
+        <v>37.1</v>
       </c>
       <c r="M104" t="inlineStr">
         <is>
@@ -28486,22 +28486,22 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>27.9</v>
+        <v>33</v>
       </c>
       <c r="Q104" t="n">
-        <v>39.2</v>
+        <v>23</v>
       </c>
       <c r="R104" t="n">
-        <v>38.7</v>
+        <v>34.3</v>
       </c>
       <c r="S104" t="n">
-        <v>40.2</v>
+        <v>47.9</v>
       </c>
       <c r="T104" t="n">
         <v>78</v>
       </c>
       <c r="U104" t="n">
-        <v>5.7</v>
+        <v>36</v>
       </c>
       <c r="V104" t="inlineStr">
         <is>
@@ -28515,7 +28515,7 @@
       </c>
       <c r="X104" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y104" t="inlineStr">
@@ -28557,134 +28557,134 @@
       </c>
       <c r="AH104" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI104" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK104" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/19, 0 HR</t>
+          <t>Last 7 games: 5/21, 1 HR</t>
         </is>
       </c>
       <c r="AL104" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.8% barrel, 9.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 4.8% barrel, 1.7 HR allowed</t>
         </is>
       </c>
       <c r="AM104" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN104" t="inlineStr">
         <is>
-          <t>7.13</t>
+          <t>6.35</t>
         </is>
       </c>
       <c r="AO104" t="inlineStr">
         <is>
-          <t>34.98</t>
+          <t>42.98</t>
         </is>
       </c>
       <c r="AP104" t="inlineStr">
         <is>
-          <t>87.86</t>
+          <t>89.93</t>
         </is>
       </c>
       <c r="AQ104" t="inlineStr">
         <is>
-          <t>98.8607</t>
+          <t>100.2229</t>
         </is>
       </c>
       <c r="AR104" t="inlineStr">
         <is>
-          <t>0.3759</t>
+          <t>0.4019</t>
         </is>
       </c>
       <c r="AS104" t="inlineStr">
         <is>
-          <t>0.1499</t>
+          <t>0.1447</t>
         </is>
       </c>
       <c r="AT104" t="inlineStr">
         <is>
-          <t>0.2812</t>
+          <t>0.3237</t>
         </is>
       </c>
       <c r="AU104" t="inlineStr">
         <is>
-          <t>71.95</t>
+          <t>72.98</t>
         </is>
       </c>
       <c r="AV104" t="inlineStr">
         <is>
-          <t>20.82</t>
+          <t>32.85</t>
         </is>
       </c>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>37.19</t>
+          <t>40.62</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>29.64</t>
+          <t>26.43</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>9.2</t>
         </is>
       </c>
       <c r="AZ104" t="inlineStr">
         <is>
-          <t>0.1288</t>
+          <t>0.134</t>
         </is>
       </c>
       <c r="BA104" t="inlineStr">
         <is>
-          <t>8.78</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="BB104" t="inlineStr">
         <is>
-          <t>37.1</t>
+          <t>41.92</t>
         </is>
       </c>
       <c r="BC104" t="inlineStr">
         <is>
-          <t>88.63</t>
+          <t>89.32</t>
         </is>
       </c>
       <c r="BD104" t="inlineStr">
         <is>
-          <t>0.3721</t>
+          <t>0.3507</t>
         </is>
       </c>
       <c r="BE104" t="inlineStr">
         <is>
-          <t>0.1551</t>
+          <t>0.1053</t>
         </is>
       </c>
       <c r="BF104" t="inlineStr">
         <is>
-          <t>30.85</t>
+          <t>16.01</t>
         </is>
       </c>
       <c r="BG104" t="inlineStr"/>
       <c r="BH104" t="inlineStr"/>
       <c r="BI104" t="inlineStr">
         <is>
-          <t>Coors Field</t>
+          <t>Citizens Bank Park</t>
         </is>
       </c>
       <c r="BJ104" t="inlineStr"/>
@@ -28695,27 +28695,27 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>592663</t>
+          <t>691458</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>J.T. Realmuto</t>
+          <t>Blaze Jordan</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-08-03T22:40:00Z</t>
+          <t>2026-08-03T23:05:00Z</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -28730,17 +28730,17 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>Andrew Alvarez</t>
+          <t>Cam Schlittler</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>674841</t>
+          <t>693645</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L105" t="n">
@@ -28758,26 +28758,26 @@
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P105" t="n">
-        <v>33</v>
+        <v>33.2</v>
       </c>
       <c r="Q105" t="n">
-        <v>23</v>
+        <v>35.4</v>
       </c>
       <c r="R105" t="n">
-        <v>34.3</v>
+        <v>38.2</v>
       </c>
       <c r="S105" t="n">
         <v>47.9</v>
       </c>
       <c r="T105" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U105" t="n">
-        <v>36</v>
+        <v>14.6</v>
       </c>
       <c r="V105" t="inlineStr">
         <is>
@@ -28816,7 +28816,7 @@
       </c>
       <c r="AC105" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD105" t="inlineStr"/>
@@ -28838,22 +28838,22 @@
       </c>
       <c r="AI105" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/21, 1 HR</t>
+          <t>Last 7 games: 5/23, 0 HR</t>
         </is>
       </c>
       <c r="AL105" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 4.8% barrel, 1.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.0% barrel, 10.8 HR allowed</t>
         </is>
       </c>
       <c r="AM105" t="inlineStr">
@@ -28863,104 +28863,104 @@
       </c>
       <c r="AN105" t="inlineStr">
         <is>
-          <t>6.35</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="AO105" t="inlineStr">
         <is>
-          <t>42.98</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="AP105" t="inlineStr">
         <is>
-          <t>89.93</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AQ105" t="inlineStr">
         <is>
-          <t>100.2229</t>
+          <t>99.9253</t>
         </is>
       </c>
       <c r="AR105" t="inlineStr">
         <is>
-          <t>0.4019</t>
+          <t>0.394</t>
         </is>
       </c>
       <c r="AS105" t="inlineStr">
         <is>
-          <t>0.1447</t>
+          <t>0.137</t>
         </is>
       </c>
       <c r="AT105" t="inlineStr">
         <is>
-          <t>0.3237</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="AU105" t="inlineStr">
         <is>
-          <t>72.98</t>
+          <t>72.7</t>
         </is>
       </c>
       <c r="AV105" t="inlineStr">
         <is>
-          <t>32.85</t>
+          <t>28.6</t>
         </is>
       </c>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>40.62</t>
+          <t>36.9</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>26.43</t>
+          <t>20.7</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr">
         <is>
-          <t>9.2</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AZ105" t="inlineStr">
         <is>
-          <t>0.134</t>
+          <t>0.112</t>
         </is>
       </c>
       <c r="BA105" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>7.99</t>
         </is>
       </c>
       <c r="BB105" t="inlineStr">
         <is>
-          <t>41.92</t>
+          <t>39.64</t>
         </is>
       </c>
       <c r="BC105" t="inlineStr">
         <is>
-          <t>89.32</t>
+          <t>88.44</t>
         </is>
       </c>
       <c r="BD105" t="inlineStr">
         <is>
-          <t>0.3507</t>
+          <t>0.3546</t>
         </is>
       </c>
       <c r="BE105" t="inlineStr">
         <is>
-          <t>0.1053</t>
+          <t>0.1372</t>
         </is>
       </c>
       <c r="BF105" t="inlineStr">
         <is>
-          <t>16.01</t>
+          <t>27.3</t>
         </is>
       </c>
       <c r="BG105" t="inlineStr"/>
       <c r="BH105" t="inlineStr"/>
       <c r="BI105" t="inlineStr">
         <is>
-          <t>Citizens Bank Park</t>
+          <t>Yankee Stadium</t>
         </is>
       </c>
       <c r="BJ105" t="inlineStr"/>
@@ -28971,12 +28971,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>691458</t>
+          <t>701675</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Blaze Jordan</t>
+          <t>Nathan Church</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -29001,7 +29001,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -29020,7 +29020,7 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>37.1</v>
+        <v>36.8</v>
       </c>
       <c r="M106" t="inlineStr">
         <is>
@@ -29034,11 +29034,11 @@
       </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P106" t="n">
-        <v>33.2</v>
+        <v>17.9</v>
       </c>
       <c r="Q106" t="n">
         <v>35.4</v>
@@ -29047,13 +29047,13 @@
         <v>38.2</v>
       </c>
       <c r="S106" t="n">
-        <v>47.9</v>
+        <v>59.8</v>
       </c>
       <c r="T106" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U106" t="n">
-        <v>14.6</v>
+        <v>21.5</v>
       </c>
       <c r="V106" t="inlineStr">
         <is>
@@ -29067,7 +29067,7 @@
       </c>
       <c r="X106" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y106" t="inlineStr">
@@ -29092,7 +29092,7 @@
       </c>
       <c r="AC106" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD106" t="inlineStr"/>
@@ -29114,7 +29114,7 @@
       </c>
       <c r="AI106" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ106" t="inlineStr">
@@ -29124,12 +29124,12 @@
       </c>
       <c r="AK106" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/23, 0 HR</t>
+          <t>Last 7 games: 5/19, 0 HR</t>
         </is>
       </c>
       <c r="AL106" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.0% barrel, 10.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.0% barrel, 10.8 HR allowed</t>
         </is>
       </c>
       <c r="AM106" t="inlineStr">
@@ -29139,67 +29139,67 @@
       </c>
       <c r="AN106" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>5.76</t>
         </is>
       </c>
       <c r="AO106" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>35.06</t>
         </is>
       </c>
       <c r="AP106" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>86.97</t>
         </is>
       </c>
       <c r="AQ106" t="inlineStr">
         <is>
-          <t>99.9253</t>
+          <t>98.1248</t>
         </is>
       </c>
       <c r="AR106" t="inlineStr">
         <is>
-          <t>0.394</t>
+          <t>0.3399</t>
         </is>
       </c>
       <c r="AS106" t="inlineStr">
         <is>
-          <t>0.137</t>
+          <t>0.1151</t>
         </is>
       </c>
       <c r="AT106" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.2729</t>
         </is>
       </c>
       <c r="AU106" t="inlineStr">
         <is>
-          <t>72.7</t>
+          <t>69.67</t>
         </is>
       </c>
       <c r="AV106" t="inlineStr">
         <is>
-          <t>28.6</t>
+          <t>8.34</t>
         </is>
       </c>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>36.9</t>
+          <t>34.5</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>20.7</t>
+          <t>19.64</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>5.9</t>
         </is>
       </c>
       <c r="AZ106" t="inlineStr">
         <is>
-          <t>0.112</t>
+          <t>0.1081</t>
         </is>
       </c>
       <c r="BA106" t="inlineStr">
@@ -29247,27 +29247,27 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>701675</t>
+          <t>663538</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Nathan Church</t>
+          <t>Nico Hoerner</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-08-03T23:05:00Z</t>
+          <t>2026-08-04T00:05:00Z</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -29277,24 +29277,12 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t>Cam Schlittler</t>
-        </is>
-      </c>
-      <c r="J107" t="inlineStr">
-        <is>
-          <t>693645</t>
-        </is>
-      </c>
-      <c r="K107" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
+      <c r="J107" t="inlineStr"/>
+      <c r="K107" t="inlineStr"/>
       <c r="L107" t="n">
         <v>36.8</v>
       </c>
@@ -29310,26 +29298,26 @@
       </c>
       <c r="O107" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P107" t="n">
-        <v>17.9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="Q107" t="n">
-        <v>35.4</v>
+        <v>41.2</v>
       </c>
       <c r="R107" t="n">
-        <v>38.2</v>
+        <v>29.8</v>
       </c>
       <c r="S107" t="n">
-        <v>59.8</v>
+        <v>71.7</v>
       </c>
       <c r="T107" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="U107" t="n">
-        <v>21.5</v>
+        <v>81.7</v>
       </c>
       <c r="V107" t="inlineStr">
         <is>
@@ -29343,7 +29331,7 @@
       </c>
       <c r="X107" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y107" t="inlineStr">
@@ -29368,7 +29356,7 @@
       </c>
       <c r="AC107" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:</t>
         </is>
       </c>
       <c r="AD107" t="inlineStr"/>
@@ -29385,27 +29373,27 @@
       </c>
       <c r="AH107" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AI107" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/19, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL107" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.0% barrel, 10.8 HR allowed</t>
+          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM107" t="inlineStr">
@@ -29415,104 +29403,80 @@
       </c>
       <c r="AN107" t="inlineStr">
         <is>
-          <t>5.76</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="AO107" t="inlineStr">
         <is>
-          <t>35.06</t>
+          <t>29.04</t>
         </is>
       </c>
       <c r="AP107" t="inlineStr">
         <is>
-          <t>86.97</t>
+          <t>86.28</t>
         </is>
       </c>
       <c r="AQ107" t="inlineStr">
         <is>
-          <t>98.1248</t>
+          <t>96.3021</t>
         </is>
       </c>
       <c r="AR107" t="inlineStr">
         <is>
-          <t>0.3399</t>
+          <t>0.3805</t>
         </is>
       </c>
       <c r="AS107" t="inlineStr">
         <is>
-          <t>0.1151</t>
+          <t>0.0836</t>
         </is>
       </c>
       <c r="AT107" t="inlineStr">
         <is>
-          <t>0.2729</t>
+          <t>0.3248</t>
         </is>
       </c>
       <c r="AU107" t="inlineStr">
         <is>
-          <t>69.67</t>
+          <t>68.33</t>
         </is>
       </c>
       <c r="AV107" t="inlineStr">
         <is>
-          <t>8.34</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>34.5</t>
+          <t>33.71</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>19.64</t>
+          <t>21.35</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr">
         <is>
-          <t>5.9</t>
+          <t>6.3</t>
         </is>
       </c>
       <c r="AZ107" t="inlineStr">
         <is>
-          <t>0.1081</t>
-        </is>
-      </c>
-      <c r="BA107" t="inlineStr">
-        <is>
-          <t>7.99</t>
-        </is>
-      </c>
-      <c r="BB107" t="inlineStr">
-        <is>
-          <t>39.64</t>
-        </is>
-      </c>
-      <c r="BC107" t="inlineStr">
-        <is>
-          <t>88.44</t>
-        </is>
-      </c>
-      <c r="BD107" t="inlineStr">
-        <is>
-          <t>0.3546</t>
-        </is>
-      </c>
-      <c r="BE107" t="inlineStr">
-        <is>
-          <t>0.1372</t>
-        </is>
-      </c>
-      <c r="BF107" t="inlineStr">
-        <is>
-          <t>27.3</t>
-        </is>
-      </c>
+          <t>0.0977</t>
+        </is>
+      </c>
+      <c r="BA107" t="inlineStr"/>
+      <c r="BB107" t="inlineStr"/>
+      <c r="BC107" t="inlineStr"/>
+      <c r="BD107" t="inlineStr"/>
+      <c r="BE107" t="inlineStr"/>
+      <c r="BF107" t="inlineStr"/>
       <c r="BG107" t="inlineStr"/>
       <c r="BH107" t="inlineStr"/>
       <c r="BI107" t="inlineStr">
         <is>
-          <t>Yankee Stadium</t>
+          <t>Wrigley Field</t>
         </is>
       </c>
       <c r="BJ107" t="inlineStr"/>
@@ -29523,27 +29487,27 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>663538</t>
+          <t>671289</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Nico Hoerner</t>
+          <t>Tyler Freeman</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-08-04T00:05:00Z</t>
+          <t>2026-08-04T00:40:00Z</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -29553,14 +29517,26 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr"/>
-      <c r="J108" t="inlineStr"/>
-      <c r="K108" t="inlineStr"/>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>Ian Seymour</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>693855</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
       <c r="L108" t="n">
-        <v>36.8</v>
+        <v>36.4</v>
       </c>
       <c r="M108" t="inlineStr">
         <is>
@@ -29574,26 +29550,26 @@
       </c>
       <c r="O108" t="inlineStr">
         <is>
-          <t>Projected Lineup, Hot Hitter/Streak</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P108" t="n">
-        <v>8.699999999999999</v>
+        <v>15.8</v>
       </c>
       <c r="Q108" t="n">
-        <v>41.2</v>
+        <v>39.2</v>
       </c>
       <c r="R108" t="n">
-        <v>29.8</v>
+        <v>38.7</v>
       </c>
       <c r="S108" t="n">
-        <v>71.7</v>
+        <v>59.8</v>
       </c>
       <c r="T108" t="n">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="U108" t="n">
-        <v>81.7</v>
+        <v>12</v>
       </c>
       <c r="V108" t="inlineStr">
         <is>
@@ -29607,7 +29583,7 @@
       </c>
       <c r="X108" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y108" t="inlineStr">
@@ -29632,7 +29608,7 @@
       </c>
       <c r="AC108" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD108" t="inlineStr"/>
@@ -29649,110 +29625,134 @@
       </c>
       <c r="AH108" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI108" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK108" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 4/20, 0 HR</t>
         </is>
       </c>
       <c r="AL108" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.8% barrel, 9.9 HR allowed</t>
         </is>
       </c>
       <c r="AM108" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN108" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="AO108" t="inlineStr">
         <is>
-          <t>29.04</t>
+          <t>37.39</t>
         </is>
       </c>
       <c r="AP108" t="inlineStr">
         <is>
-          <t>86.28</t>
+          <t>88.42</t>
         </is>
       </c>
       <c r="AQ108" t="inlineStr">
         <is>
-          <t>96.3021</t>
+          <t>98.7495</t>
         </is>
       </c>
       <c r="AR108" t="inlineStr">
         <is>
-          <t>0.3805</t>
+          <t>0.3572</t>
         </is>
       </c>
       <c r="AS108" t="inlineStr">
         <is>
-          <t>0.0836</t>
+          <t>0.088</t>
         </is>
       </c>
       <c r="AT108" t="inlineStr">
         <is>
-          <t>0.3248</t>
+          <t>0.3152</t>
         </is>
       </c>
       <c r="AU108" t="inlineStr">
         <is>
-          <t>68.33</t>
+          <t>70.74</t>
         </is>
       </c>
       <c r="AV108" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>13.1</t>
         </is>
       </c>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>33.71</t>
+          <t>33.6</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>21.35</t>
+          <t>20.31</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr">
         <is>
-          <t>6.3</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="AZ108" t="inlineStr">
         <is>
-          <t>0.0977</t>
-        </is>
-      </c>
-      <c r="BA108" t="inlineStr"/>
-      <c r="BB108" t="inlineStr"/>
-      <c r="BC108" t="inlineStr"/>
-      <c r="BD108" t="inlineStr"/>
-      <c r="BE108" t="inlineStr"/>
-      <c r="BF108" t="inlineStr"/>
+          <t>0.0723</t>
+        </is>
+      </c>
+      <c r="BA108" t="inlineStr">
+        <is>
+          <t>8.78</t>
+        </is>
+      </c>
+      <c r="BB108" t="inlineStr">
+        <is>
+          <t>37.1</t>
+        </is>
+      </c>
+      <c r="BC108" t="inlineStr">
+        <is>
+          <t>88.63</t>
+        </is>
+      </c>
+      <c r="BD108" t="inlineStr">
+        <is>
+          <t>0.3721</t>
+        </is>
+      </c>
+      <c r="BE108" t="inlineStr">
+        <is>
+          <t>0.1551</t>
+        </is>
+      </c>
+      <c r="BF108" t="inlineStr">
+        <is>
+          <t>30.85</t>
+        </is>
+      </c>
       <c r="BG108" t="inlineStr"/>
       <c r="BH108" t="inlineStr"/>
       <c r="BI108" t="inlineStr">
         <is>
-          <t>Wrigley Field</t>
+          <t>Coors Field</t>
         </is>
       </c>
       <c r="BJ108" t="inlineStr"/>
@@ -29763,12 +29763,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>671289</t>
+          <t>681198</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Tyler Freeman</t>
+          <t>TJ Rumfield</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -29793,7 +29793,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -29812,7 +29812,7 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>36.4</v>
+        <v>36.2</v>
       </c>
       <c r="M109" t="inlineStr">
         <is>
@@ -29826,11 +29826,11 @@
       </c>
       <c r="O109" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P109" t="n">
-        <v>15.8</v>
+        <v>12.6</v>
       </c>
       <c r="Q109" t="n">
         <v>39.2</v>
@@ -29839,13 +29839,13 @@
         <v>38.7</v>
       </c>
       <c r="S109" t="n">
-        <v>59.8</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T109" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U109" t="n">
-        <v>12</v>
+        <v>18.2</v>
       </c>
       <c r="V109" t="inlineStr">
         <is>
@@ -29859,7 +29859,7 @@
       </c>
       <c r="X109" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y109" t="inlineStr">
@@ -29884,7 +29884,7 @@
       </c>
       <c r="AC109" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD109" t="inlineStr"/>
@@ -29901,12 +29901,12 @@
       </c>
       <c r="AH109" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI109" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ109" t="inlineStr">
@@ -29916,12 +29916,12 @@
       </c>
       <c r="AK109" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/20, 0 HR</t>
+          <t>Last 7 games: 7/29, 0 HR</t>
         </is>
       </c>
       <c r="AL109" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.8% barrel, 9.9 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.8% barrel, 9.9 HR allowed</t>
         </is>
       </c>
       <c r="AM109" t="inlineStr">
@@ -29931,67 +29931,67 @@
       </c>
       <c r="AN109" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AO109" t="inlineStr">
         <is>
-          <t>37.39</t>
+          <t>27.4</t>
         </is>
       </c>
       <c r="AP109" t="inlineStr">
         <is>
-          <t>88.42</t>
+          <t>83.6</t>
         </is>
       </c>
       <c r="AQ109" t="inlineStr">
         <is>
-          <t>98.7495</t>
+          <t>96.1088</t>
         </is>
       </c>
       <c r="AR109" t="inlineStr">
         <is>
-          <t>0.3572</t>
+          <t>0.378</t>
         </is>
       </c>
       <c r="AS109" t="inlineStr">
         <is>
-          <t>0.088</t>
+          <t>0.125</t>
         </is>
       </c>
       <c r="AT109" t="inlineStr">
         <is>
-          <t>0.3152</t>
+          <t>0.321</t>
         </is>
       </c>
       <c r="AU109" t="inlineStr">
         <is>
-          <t>70.74</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="AV109" t="inlineStr">
         <is>
-          <t>13.1</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>33.6</t>
+          <t>43.4</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>20.31</t>
+          <t>27.4</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="AZ109" t="inlineStr">
         <is>
-          <t>0.0723</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="BA109" t="inlineStr">
@@ -30039,27 +30039,27 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>681198</t>
+          <t>593428</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>TJ Rumfield</t>
+          <t>Xander Bogaerts</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-08-04T00:40:00Z</t>
+          <t>2026-08-04T01:40:00Z</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -30069,22 +30069,22 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>Ian Seymour</t>
+          <t>Brandon Pfaadt</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>693855</t>
+          <t>694297</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L110" t="n">
@@ -30106,22 +30106,22 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>12.6</v>
+        <v>26.6</v>
       </c>
       <c r="Q110" t="n">
-        <v>39.2</v>
+        <v>45.9</v>
       </c>
       <c r="R110" t="n">
-        <v>38.7</v>
+        <v>28.2</v>
       </c>
       <c r="S110" t="n">
-        <v>81.90000000000001</v>
+        <v>47.9</v>
       </c>
       <c r="T110" t="n">
         <v>50</v>
       </c>
       <c r="U110" t="n">
-        <v>18.2</v>
+        <v>19.5</v>
       </c>
       <c r="V110" t="inlineStr">
         <is>
@@ -30135,7 +30135,7 @@
       </c>
       <c r="X110" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y110" t="inlineStr">
@@ -30160,7 +30160,7 @@
       </c>
       <c r="AC110" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD110" t="inlineStr"/>
@@ -30177,12 +30177,12 @@
       </c>
       <c r="AH110" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI110" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ110" t="inlineStr">
@@ -30192,119 +30192,119 @@
       </c>
       <c r="AK110" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/29, 0 HR</t>
+          <t>Last 7 games: 6/24, 0 HR</t>
         </is>
       </c>
       <c r="AL110" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.8% barrel, 9.9 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 9.6% barrel, 13.4 HR allowed</t>
         </is>
       </c>
       <c r="AM110" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN110" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>6.13</t>
         </is>
       </c>
       <c r="AO110" t="inlineStr">
         <is>
-          <t>27.4</t>
+          <t>38.92</t>
         </is>
       </c>
       <c r="AP110" t="inlineStr">
         <is>
-          <t>83.6</t>
+          <t>88.44</t>
         </is>
       </c>
       <c r="AQ110" t="inlineStr">
         <is>
-          <t>96.1088</t>
+          <t>99.74</t>
         </is>
       </c>
       <c r="AR110" t="inlineStr">
         <is>
-          <t>0.378</t>
+          <t>0.3808</t>
         </is>
       </c>
       <c r="AS110" t="inlineStr">
         <is>
-          <t>0.125</t>
+          <t>0.132</t>
         </is>
       </c>
       <c r="AT110" t="inlineStr">
         <is>
-          <t>0.321</t>
+          <t>0.3186</t>
         </is>
       </c>
       <c r="AU110" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>72.31</t>
         </is>
       </c>
       <c r="AV110" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>27.59</t>
         </is>
       </c>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>43.4</t>
+          <t>44.15</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>27.4</t>
+          <t>23.41</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="AZ110" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.1091</t>
         </is>
       </c>
       <c r="BA110" t="inlineStr">
         <is>
-          <t>8.78</t>
+          <t>9.57</t>
         </is>
       </c>
       <c r="BB110" t="inlineStr">
         <is>
-          <t>37.1</t>
+          <t>39.78</t>
         </is>
       </c>
       <c r="BC110" t="inlineStr">
         <is>
-          <t>88.63</t>
+          <t>89.4</t>
         </is>
       </c>
       <c r="BD110" t="inlineStr">
         <is>
-          <t>0.3721</t>
+          <t>0.4275</t>
         </is>
       </c>
       <c r="BE110" t="inlineStr">
         <is>
-          <t>0.1551</t>
+          <t>0.1715</t>
         </is>
       </c>
       <c r="BF110" t="inlineStr">
         <is>
-          <t>30.85</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="BG110" t="inlineStr"/>
       <c r="BH110" t="inlineStr"/>
       <c r="BI110" t="inlineStr">
         <is>
-          <t>Coors Field</t>
+          <t>Chase Field</t>
         </is>
       </c>
       <c r="BJ110" t="inlineStr"/>
@@ -30315,27 +30315,27 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>593428</t>
+          <t>663968</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Xander Bogaerts</t>
+          <t>Jake Mangum</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-08-04T01:40:00Z</t>
+          <t>2026-08-03T23:40:00Z</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -30345,17 +30345,17 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>Brandon Pfaadt</t>
+          <t>Brandon Sproat</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>694297</t>
+          <t>687075</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
@@ -30364,7 +30364,7 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>36.2</v>
+        <v>36</v>
       </c>
       <c r="M111" t="inlineStr">
         <is>
@@ -30378,26 +30378,26 @@
       </c>
       <c r="O111" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P111" t="n">
-        <v>26.6</v>
+        <v>5.2</v>
       </c>
       <c r="Q111" t="n">
-        <v>45.9</v>
+        <v>36.5</v>
       </c>
       <c r="R111" t="n">
-        <v>28.2</v>
+        <v>27.6</v>
       </c>
       <c r="S111" t="n">
-        <v>47.9</v>
+        <v>88.7</v>
       </c>
       <c r="T111" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U111" t="n">
-        <v>19.5</v>
+        <v>45.3</v>
       </c>
       <c r="V111" t="inlineStr">
         <is>
@@ -30411,7 +30411,7 @@
       </c>
       <c r="X111" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y111" t="inlineStr">
@@ -30453,27 +30453,27 @@
       </c>
       <c r="AH111" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI111" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/24, 0 HR</t>
+          <t>Last 7 games: 9/30, 1 HR</t>
         </is>
       </c>
       <c r="AL111" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 9.6% barrel, 13.4 HR allowed</t>
+          <t>switch hitter; pitcher baseline 7.3% barrel, 11.9 HR allowed</t>
         </is>
       </c>
       <c r="AM111" t="inlineStr">
@@ -30483,104 +30483,104 @@
       </c>
       <c r="AN111" t="inlineStr">
         <is>
-          <t>6.13</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="AO111" t="inlineStr">
         <is>
-          <t>38.92</t>
+          <t>28.01</t>
         </is>
       </c>
       <c r="AP111" t="inlineStr">
         <is>
-          <t>88.44</t>
+          <t>85.76</t>
         </is>
       </c>
       <c r="AQ111" t="inlineStr">
         <is>
-          <t>99.74</t>
+          <t>96.4016</t>
         </is>
       </c>
       <c r="AR111" t="inlineStr">
         <is>
-          <t>0.3808</t>
+          <t>0.3297</t>
         </is>
       </c>
       <c r="AS111" t="inlineStr">
         <is>
-          <t>0.132</t>
+          <t>0.0745</t>
         </is>
       </c>
       <c r="AT111" t="inlineStr">
         <is>
-          <t>0.3186</t>
+          <t>0.283</t>
         </is>
       </c>
       <c r="AU111" t="inlineStr">
         <is>
-          <t>72.31</t>
+          <t>67.44</t>
         </is>
       </c>
       <c r="AV111" t="inlineStr">
         <is>
-          <t>27.59</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>44.15</t>
+          <t>27.72</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>23.41</t>
+          <t>14.65</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AZ111" t="inlineStr">
         <is>
-          <t>0.1091</t>
+          <t>0.0748</t>
         </is>
       </c>
       <c r="BA111" t="inlineStr">
         <is>
-          <t>9.57</t>
+          <t>7.32</t>
         </is>
       </c>
       <c r="BB111" t="inlineStr">
         <is>
-          <t>39.78</t>
+          <t>41.61</t>
         </is>
       </c>
       <c r="BC111" t="inlineStr">
         <is>
-          <t>89.4</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="BD111" t="inlineStr">
         <is>
-          <t>0.4275</t>
+          <t>0.3962</t>
         </is>
       </c>
       <c r="BE111" t="inlineStr">
         <is>
-          <t>0.1715</t>
+          <t>0.1472</t>
         </is>
       </c>
       <c r="BF111" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="BG111" t="inlineStr"/>
       <c r="BH111" t="inlineStr"/>
       <c r="BI111" t="inlineStr">
         <is>
-          <t>Chase Field</t>
+          <t>American Family Field</t>
         </is>
       </c>
       <c r="BJ111" t="inlineStr"/>
@@ -30591,12 +30591,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>663968</t>
+          <t>694378</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Jake Mangum</t>
+          <t>Jacob Gonzalez</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -30621,7 +30621,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -30654,26 +30654,26 @@
       </c>
       <c r="O112" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P112" t="n">
-        <v>5.2</v>
+        <v>25.3</v>
       </c>
       <c r="Q112" t="n">
-        <v>36.5</v>
+        <v>37.8</v>
       </c>
       <c r="R112" t="n">
         <v>27.6</v>
       </c>
       <c r="S112" t="n">
-        <v>88.7</v>
+        <v>47.9</v>
       </c>
       <c r="T112" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U112" t="n">
-        <v>45.3</v>
+        <v>10.6</v>
       </c>
       <c r="V112" t="inlineStr">
         <is>
@@ -30687,7 +30687,7 @@
       </c>
       <c r="X112" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y112" t="inlineStr">
@@ -30712,7 +30712,7 @@
       </c>
       <c r="AC112" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD112" t="inlineStr"/>
@@ -30729,27 +30729,27 @@
       </c>
       <c r="AH112" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI112" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK112" t="inlineStr">
         <is>
-          <t>Last 7 games: 9/30, 1 HR</t>
+          <t>Last 7 games: 4/21, 0 HR</t>
         </is>
       </c>
       <c r="AL112" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 7.3% barrel, 11.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.3% barrel, 11.9 HR allowed</t>
         </is>
       </c>
       <c r="AM112" t="inlineStr">
@@ -30759,67 +30759,67 @@
       </c>
       <c r="AN112" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="AO112" t="inlineStr">
         <is>
-          <t>28.01</t>
+          <t>40.8</t>
         </is>
       </c>
       <c r="AP112" t="inlineStr">
         <is>
-          <t>85.76</t>
+          <t>88.9</t>
         </is>
       </c>
       <c r="AQ112" t="inlineStr">
         <is>
-          <t>96.4016</t>
+          <t>99.3194</t>
         </is>
       </c>
       <c r="AR112" t="inlineStr">
         <is>
-          <t>0.3297</t>
+          <t>0.404</t>
         </is>
       </c>
       <c r="AS112" t="inlineStr">
         <is>
-          <t>0.0745</t>
+          <t>0.141</t>
         </is>
       </c>
       <c r="AT112" t="inlineStr">
         <is>
-          <t>0.283</t>
+          <t>0.316</t>
         </is>
       </c>
       <c r="AU112" t="inlineStr">
         <is>
-          <t>67.44</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AV112" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>12.2</t>
         </is>
       </c>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>27.72</t>
+          <t>38.4</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>14.65</t>
+          <t>29.3</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AZ112" t="inlineStr">
         <is>
-          <t>0.0748</t>
+          <t>0.145</t>
         </is>
       </c>
       <c r="BA112" t="inlineStr">
@@ -30867,27 +30867,27 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>694378</t>
+          <t>681082</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Jacob Gonzalez</t>
+          <t>Bryson Stott</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-08-03T23:40:00Z</t>
+          <t>2026-08-03T22:40:00Z</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -30897,26 +30897,26 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>Brandon Sproat</t>
+          <t>Andrew Alvarez</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>687075</t>
+          <t>674841</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L113" t="n">
-        <v>36</v>
+        <v>35.2</v>
       </c>
       <c r="M113" t="inlineStr">
         <is>
@@ -30930,26 +30930,26 @@
       </c>
       <c r="O113" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P113" t="n">
-        <v>25.3</v>
+        <v>27.5</v>
       </c>
       <c r="Q113" t="n">
-        <v>37.8</v>
+        <v>23</v>
       </c>
       <c r="R113" t="n">
-        <v>27.6</v>
+        <v>34.3</v>
       </c>
       <c r="S113" t="n">
-        <v>47.9</v>
+        <v>59.8</v>
       </c>
       <c r="T113" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U113" t="n">
-        <v>10.6</v>
+        <v>52.8</v>
       </c>
       <c r="V113" t="inlineStr">
         <is>
@@ -30963,7 +30963,7 @@
       </c>
       <c r="X113" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y113" t="inlineStr">
@@ -30988,7 +30988,7 @@
       </c>
       <c r="AC113" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD113" t="inlineStr"/>
@@ -31005,27 +31005,27 @@
       </c>
       <c r="AH113" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI113" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/21, 0 HR</t>
+          <t>Contact streak: 7/20 over last 7 games</t>
         </is>
       </c>
       <c r="AL113" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.3% barrel, 11.9 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 4.8% barrel, 1.7 HR allowed</t>
         </is>
       </c>
       <c r="AM113" t="inlineStr">
@@ -31035,104 +31035,104 @@
       </c>
       <c r="AN113" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AO113" t="inlineStr">
         <is>
-          <t>40.8</t>
+          <t>36.08</t>
         </is>
       </c>
       <c r="AP113" t="inlineStr">
         <is>
-          <t>88.9</t>
+          <t>88.79</t>
         </is>
       </c>
       <c r="AQ113" t="inlineStr">
         <is>
-          <t>99.3194</t>
+          <t>98.5788</t>
         </is>
       </c>
       <c r="AR113" t="inlineStr">
         <is>
-          <t>0.404</t>
+          <t>0.4014</t>
         </is>
       </c>
       <c r="AS113" t="inlineStr">
         <is>
-          <t>0.141</t>
+          <t>0.1432</t>
         </is>
       </c>
       <c r="AT113" t="inlineStr">
         <is>
-          <t>0.316</t>
+          <t>0.3193</t>
         </is>
       </c>
       <c r="AU113" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>69.79</t>
         </is>
       </c>
       <c r="AV113" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>6.75</t>
         </is>
       </c>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>38.4</t>
+          <t>35.08</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>29.3</t>
+          <t>29.2</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="AZ113" t="inlineStr">
         <is>
-          <t>0.145</t>
+          <t>0.1487</t>
         </is>
       </c>
       <c r="BA113" t="inlineStr">
         <is>
-          <t>7.32</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="BB113" t="inlineStr">
         <is>
-          <t>41.61</t>
+          <t>41.92</t>
         </is>
       </c>
       <c r="BC113" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>89.32</t>
         </is>
       </c>
       <c r="BD113" t="inlineStr">
         <is>
-          <t>0.3962</t>
+          <t>0.3507</t>
         </is>
       </c>
       <c r="BE113" t="inlineStr">
         <is>
-          <t>0.1472</t>
+          <t>0.1053</t>
         </is>
       </c>
       <c r="BF113" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>16.01</t>
         </is>
       </c>
       <c r="BG113" t="inlineStr"/>
       <c r="BH113" t="inlineStr"/>
       <c r="BI113" t="inlineStr">
         <is>
-          <t>American Family Field</t>
+          <t>Citizens Bank Park</t>
         </is>
       </c>
       <c r="BJ113" t="inlineStr"/>
@@ -31143,27 +31143,27 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>681082</t>
+          <t>676609</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Bryson Stott</t>
+          <t>Jose Caballero</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-08-03T22:40:00Z</t>
+          <t>2026-08-03T23:05:00Z</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -31173,26 +31173,26 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>Andrew Alvarez</t>
+          <t>Michael McGreevy</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>674841</t>
+          <t>700241</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L114" t="n">
-        <v>35.2</v>
+        <v>35.1</v>
       </c>
       <c r="M114" t="inlineStr">
         <is>
@@ -31210,22 +31210,22 @@
         </is>
       </c>
       <c r="P114" t="n">
-        <v>27.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Q114" t="n">
-        <v>23</v>
+        <v>55.6</v>
       </c>
       <c r="R114" t="n">
-        <v>34.3</v>
+        <v>38.2</v>
       </c>
       <c r="S114" t="n">
-        <v>59.8</v>
+        <v>47.9</v>
       </c>
       <c r="T114" t="n">
         <v>50</v>
       </c>
       <c r="U114" t="n">
-        <v>52.8</v>
+        <v>43.2</v>
       </c>
       <c r="V114" t="inlineStr">
         <is>
@@ -31239,7 +31239,7 @@
       </c>
       <c r="X114" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y114" t="inlineStr">
@@ -31281,12 +31281,12 @@
       </c>
       <c r="AH114" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI114" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ114" t="inlineStr">
@@ -31296,12 +31296,12 @@
       </c>
       <c r="AK114" t="inlineStr">
         <is>
-          <t>Contact streak: 7/20 over last 7 games</t>
+          <t>Last 7 games: 6/21, 1 HR</t>
         </is>
       </c>
       <c r="AL114" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 4.8% barrel, 1.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 10.0% barrel, 14.1 HR allowed</t>
         </is>
       </c>
       <c r="AM114" t="inlineStr">
@@ -31311,104 +31311,104 @@
       </c>
       <c r="AN114" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>4.36</t>
         </is>
       </c>
       <c r="AO114" t="inlineStr">
         <is>
-          <t>36.08</t>
+          <t>26.4</t>
         </is>
       </c>
       <c r="AP114" t="inlineStr">
         <is>
-          <t>88.79</t>
+          <t>84.46</t>
         </is>
       </c>
       <c r="AQ114" t="inlineStr">
         <is>
-          <t>98.5788</t>
+          <t>96.3388</t>
         </is>
       </c>
       <c r="AR114" t="inlineStr">
         <is>
-          <t>0.4014</t>
+          <t>0.3362</t>
         </is>
       </c>
       <c r="AS114" t="inlineStr">
         <is>
-          <t>0.1432</t>
+          <t>0.1087</t>
         </is>
       </c>
       <c r="AT114" t="inlineStr">
         <is>
-          <t>0.3193</t>
+          <t>0.2836</t>
         </is>
       </c>
       <c r="AU114" t="inlineStr">
         <is>
-          <t>69.79</t>
+          <t>68.82</t>
         </is>
       </c>
       <c r="AV114" t="inlineStr">
         <is>
-          <t>6.75</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>35.08</t>
+          <t>41.46</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>29.2</t>
+          <t>21.1</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>9.2</t>
         </is>
       </c>
       <c r="AZ114" t="inlineStr">
         <is>
-          <t>0.1487</t>
+          <t>0.1334</t>
         </is>
       </c>
       <c r="BA114" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>9.99</t>
         </is>
       </c>
       <c r="BB114" t="inlineStr">
         <is>
-          <t>41.92</t>
+          <t>41.85</t>
         </is>
       </c>
       <c r="BC114" t="inlineStr">
         <is>
-          <t>89.32</t>
+          <t>90.29</t>
         </is>
       </c>
       <c r="BD114" t="inlineStr">
         <is>
-          <t>0.3507</t>
+          <t>0.4864</t>
         </is>
       </c>
       <c r="BE114" t="inlineStr">
         <is>
-          <t>0.1053</t>
+          <t>0.2012</t>
         </is>
       </c>
       <c r="BF114" t="inlineStr">
         <is>
-          <t>16.01</t>
+          <t>25.71</t>
         </is>
       </c>
       <c r="BG114" t="inlineStr"/>
       <c r="BH114" t="inlineStr"/>
       <c r="BI114" t="inlineStr">
         <is>
-          <t>Citizens Bank Park</t>
+          <t>Yankee Stadium</t>
         </is>
       </c>
       <c r="BJ114" t="inlineStr"/>
@@ -31419,24 +31419,24 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>676609</t>
+          <t>691026</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Jose Caballero</t>
+          <t>Masyn Winn</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
           <t>NYY</t>
         </is>
       </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>STL</t>
-        </is>
-      </c>
       <c r="F115" t="inlineStr">
         <is>
           <t>2026-08-03T23:05:00Z</t>
@@ -31449,17 +31449,17 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>Michael McGreevy</t>
+          <t>Cam Schlittler</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>700241</t>
+          <t>693645</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
@@ -31468,7 +31468,7 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>35.1</v>
+        <v>35</v>
       </c>
       <c r="M115" t="inlineStr">
         <is>
@@ -31486,22 +31486,22 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>8.199999999999999</v>
+        <v>15</v>
       </c>
       <c r="Q115" t="n">
-        <v>55.6</v>
+        <v>35.4</v>
       </c>
       <c r="R115" t="n">
         <v>38.2</v>
       </c>
       <c r="S115" t="n">
-        <v>47.9</v>
+        <v>71.7</v>
       </c>
       <c r="T115" t="n">
         <v>50</v>
       </c>
       <c r="U115" t="n">
-        <v>43.2</v>
+        <v>25.8</v>
       </c>
       <c r="V115" t="inlineStr">
         <is>
@@ -31515,7 +31515,7 @@
       </c>
       <c r="X115" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y115" t="inlineStr">
@@ -31557,27 +31557,27 @@
       </c>
       <c r="AH115" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI115" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/21, 1 HR</t>
+          <t>Last 7 games: 7/24, 0 HR</t>
         </is>
       </c>
       <c r="AL115" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 10.0% barrel, 14.1 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.0% barrel, 10.8 HR allowed</t>
         </is>
       </c>
       <c r="AM115" t="inlineStr">
@@ -31587,97 +31587,97 @@
       </c>
       <c r="AN115" t="inlineStr">
         <is>
-          <t>4.36</t>
+          <t>3.61</t>
         </is>
       </c>
       <c r="AO115" t="inlineStr">
         <is>
-          <t>26.4</t>
+          <t>35.3</t>
         </is>
       </c>
       <c r="AP115" t="inlineStr">
         <is>
-          <t>84.46</t>
+          <t>88.09</t>
         </is>
       </c>
       <c r="AQ115" t="inlineStr">
         <is>
-          <t>96.3388</t>
+          <t>98.6916</t>
         </is>
       </c>
       <c r="AR115" t="inlineStr">
         <is>
-          <t>0.3362</t>
+          <t>0.333</t>
         </is>
       </c>
       <c r="AS115" t="inlineStr">
         <is>
-          <t>0.1087</t>
+          <t>0.086</t>
         </is>
       </c>
       <c r="AT115" t="inlineStr">
         <is>
-          <t>0.2836</t>
+          <t>0.2965</t>
         </is>
       </c>
       <c r="AU115" t="inlineStr">
         <is>
-          <t>68.82</t>
+          <t>71.17</t>
         </is>
       </c>
       <c r="AV115" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>15.42</t>
         </is>
       </c>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>41.46</t>
+          <t>32.11</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>21.1</t>
+          <t>21.32</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr">
         <is>
-          <t>9.2</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AZ115" t="inlineStr">
         <is>
-          <t>0.1334</t>
+          <t>0.0897</t>
         </is>
       </c>
       <c r="BA115" t="inlineStr">
         <is>
-          <t>9.99</t>
+          <t>7.99</t>
         </is>
       </c>
       <c r="BB115" t="inlineStr">
         <is>
-          <t>41.85</t>
+          <t>39.64</t>
         </is>
       </c>
       <c r="BC115" t="inlineStr">
         <is>
-          <t>90.29</t>
+          <t>88.44</t>
         </is>
       </c>
       <c r="BD115" t="inlineStr">
         <is>
-          <t>0.4864</t>
+          <t>0.3546</t>
         </is>
       </c>
       <c r="BE115" t="inlineStr">
         <is>
-          <t>0.2012</t>
+          <t>0.1372</t>
         </is>
       </c>
       <c r="BF115" t="inlineStr">
         <is>
-          <t>25.71</t>
+          <t>27.3</t>
         </is>
       </c>
       <c r="BG115" t="inlineStr"/>
@@ -31695,27 +31695,27 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>691026</t>
+          <t>800325</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Masyn Winn</t>
+          <t>Luis Lara</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-08-03T23:05:00Z</t>
+          <t>2026-08-03T23:40:00Z</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -31725,17 +31725,17 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>Cam Schlittler</t>
+          <t>Bubba Chandler</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>693645</t>
+          <t>696149</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
@@ -31744,7 +31744,7 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>35</v>
+        <v>34.9</v>
       </c>
       <c r="M116" t="inlineStr">
         <is>
@@ -31758,26 +31758,26 @@
       </c>
       <c r="O116" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P116" t="n">
-        <v>15</v>
+        <v>19.4</v>
       </c>
       <c r="Q116" t="n">
-        <v>35.4</v>
+        <v>34.2</v>
       </c>
       <c r="R116" t="n">
-        <v>38.2</v>
+        <v>27.6</v>
       </c>
       <c r="S116" t="n">
-        <v>71.7</v>
+        <v>59.8</v>
       </c>
       <c r="T116" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U116" t="n">
-        <v>25.8</v>
+        <v>21.1</v>
       </c>
       <c r="V116" t="inlineStr">
         <is>
@@ -31791,7 +31791,7 @@
       </c>
       <c r="X116" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y116" t="inlineStr">
@@ -31816,7 +31816,7 @@
       </c>
       <c r="AC116" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD116" t="inlineStr"/>
@@ -31833,12 +31833,12 @@
       </c>
       <c r="AH116" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI116" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ116" t="inlineStr">
@@ -31848,12 +31848,12 @@
       </c>
       <c r="AK116" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/24, 0 HR</t>
+          <t>Last 7 games: 6/23, 0 HR</t>
         </is>
       </c>
       <c r="AL116" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.0% barrel, 10.8 HR allowed</t>
+          <t>switch hitter; pitcher baseline 7.2% barrel, 7.6 HR allowed</t>
         </is>
       </c>
       <c r="AM116" t="inlineStr">
@@ -31863,27 +31863,27 @@
       </c>
       <c r="AN116" t="inlineStr">
         <is>
-          <t>3.61</t>
+          <t>4.8</t>
         </is>
       </c>
       <c r="AO116" t="inlineStr">
         <is>
-          <t>35.3</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="AP116" t="inlineStr">
         <is>
-          <t>88.09</t>
+          <t>88.3</t>
         </is>
       </c>
       <c r="AQ116" t="inlineStr">
         <is>
-          <t>98.6916</t>
+          <t>98.1872</t>
         </is>
       </c>
       <c r="AR116" t="inlineStr">
         <is>
-          <t>0.333</t>
+          <t>0.376</t>
         </is>
       </c>
       <c r="AS116" t="inlineStr">
@@ -31893,74 +31893,74 @@
       </c>
       <c r="AT116" t="inlineStr">
         <is>
-          <t>0.2965</t>
+          <t>0.341</t>
         </is>
       </c>
       <c r="AU116" t="inlineStr">
         <is>
-          <t>71.17</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AV116" t="inlineStr">
         <is>
-          <t>15.42</t>
+          <t>16.7</t>
         </is>
       </c>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>32.11</t>
+          <t>33.3</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>21.32</t>
+          <t>21.4</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ116" t="inlineStr">
         <is>
-          <t>0.0897</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="BA116" t="inlineStr">
         <is>
-          <t>7.99</t>
+          <t>7.16</t>
         </is>
       </c>
       <c r="BB116" t="inlineStr">
         <is>
-          <t>39.64</t>
+          <t>37.97</t>
         </is>
       </c>
       <c r="BC116" t="inlineStr">
         <is>
-          <t>88.44</t>
+          <t>89.22</t>
         </is>
       </c>
       <c r="BD116" t="inlineStr">
         <is>
-          <t>0.3546</t>
+          <t>0.3779</t>
         </is>
       </c>
       <c r="BE116" t="inlineStr">
         <is>
-          <t>0.1372</t>
+          <t>0.1532</t>
         </is>
       </c>
       <c r="BF116" t="inlineStr">
         <is>
-          <t>27.3</t>
+          <t>26.93</t>
         </is>
       </c>
       <c r="BG116" t="inlineStr"/>
       <c r="BH116" t="inlineStr"/>
       <c r="BI116" t="inlineStr">
         <is>
-          <t>Yankee Stadium</t>
+          <t>American Family Field</t>
         </is>
       </c>
       <c r="BJ116" t="inlineStr"/>
@@ -31971,27 +31971,27 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>800325</t>
+          <t>670764</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Luis Lara</t>
+          <t>Taylor Walls</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-08-03T23:40:00Z</t>
+          <t>2026-08-04T00:40:00Z</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -32006,12 +32006,12 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>Bubba Chandler</t>
+          <t>Michael Lorenzen</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>696149</t>
+          <t>547179</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
@@ -32038,13 +32038,13 @@
         </is>
       </c>
       <c r="P117" t="n">
-        <v>19.4</v>
+        <v>5.3</v>
       </c>
       <c r="Q117" t="n">
-        <v>34.2</v>
+        <v>51.1</v>
       </c>
       <c r="R117" t="n">
-        <v>27.6</v>
+        <v>38.7</v>
       </c>
       <c r="S117" t="n">
         <v>59.8</v>
@@ -32053,7 +32053,7 @@
         <v>75</v>
       </c>
       <c r="U117" t="n">
-        <v>21.1</v>
+        <v>0</v>
       </c>
       <c r="V117" t="inlineStr">
         <is>
@@ -32092,7 +32092,7 @@
       </c>
       <c r="AC117" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD117" t="inlineStr"/>
@@ -32109,12 +32109,12 @@
       </c>
       <c r="AH117" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AI117" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AJ117" t="inlineStr">
@@ -32124,12 +32124,12 @@
       </c>
       <c r="AK117" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/23, 0 HR</t>
+          <t>Last 7 games: 0/14, 0 HR</t>
         </is>
       </c>
       <c r="AL117" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 7.2% barrel, 7.6 HR allowed</t>
+          <t>switch hitter; pitcher baseline 8.9% barrel, 18.7 HR allowed</t>
         </is>
       </c>
       <c r="AM117" t="inlineStr">
@@ -32139,104 +32139,104 @@
       </c>
       <c r="AN117" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="AO117" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>23.39</t>
         </is>
       </c>
       <c r="AP117" t="inlineStr">
         <is>
-          <t>88.3</t>
+          <t>85.67</t>
         </is>
       </c>
       <c r="AQ117" t="inlineStr">
         <is>
-          <t>98.1872</t>
+          <t>95.3063</t>
         </is>
       </c>
       <c r="AR117" t="inlineStr">
         <is>
-          <t>0.376</t>
+          <t>0.2663</t>
         </is>
       </c>
       <c r="AS117" t="inlineStr">
         <is>
-          <t>0.086</t>
+          <t>0.0759</t>
         </is>
       </c>
       <c r="AT117" t="inlineStr">
         <is>
-          <t>0.341</t>
+          <t>0.2491</t>
         </is>
       </c>
       <c r="AU117" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>68.42</t>
         </is>
       </c>
       <c r="AV117" t="inlineStr">
         <is>
-          <t>16.7</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>33.3</t>
+          <t>36.79</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>21.4</t>
+          <t>29.05</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="AZ117" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.078</t>
         </is>
       </c>
       <c r="BA117" t="inlineStr">
         <is>
-          <t>7.16</t>
+          <t>8.94</t>
         </is>
       </c>
       <c r="BB117" t="inlineStr">
         <is>
-          <t>37.97</t>
+          <t>44.1</t>
         </is>
       </c>
       <c r="BC117" t="inlineStr">
         <is>
-          <t>89.22</t>
+          <t>90.42</t>
         </is>
       </c>
       <c r="BD117" t="inlineStr">
         <is>
-          <t>0.3779</t>
+          <t>0.4664</t>
         </is>
       </c>
       <c r="BE117" t="inlineStr">
         <is>
-          <t>0.1532</t>
+          <t>0.1826</t>
         </is>
       </c>
       <c r="BF117" t="inlineStr">
         <is>
-          <t>26.93</t>
+          <t>25.59</t>
         </is>
       </c>
       <c r="BG117" t="inlineStr"/>
       <c r="BH117" t="inlineStr"/>
       <c r="BI117" t="inlineStr">
         <is>
-          <t>American Family Field</t>
+          <t>Coors Field</t>
         </is>
       </c>
       <c r="BJ117" t="inlineStr"/>
@@ -32247,27 +32247,27 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>670764</t>
+          <t>693304</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Taylor Walls</t>
+          <t>Nick Gonzales</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-08-04T00:40:00Z</t>
+          <t>2026-08-03T23:40:00Z</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -32277,17 +32277,17 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>Michael Lorenzen</t>
+          <t>Brandon Sproat</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>547179</t>
+          <t>687075</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
@@ -32296,7 +32296,7 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>34.9</v>
+        <v>34.6</v>
       </c>
       <c r="M118" t="inlineStr">
         <is>
@@ -32310,26 +32310,26 @@
       </c>
       <c r="O118" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P118" t="n">
-        <v>5.3</v>
+        <v>16.6</v>
       </c>
       <c r="Q118" t="n">
-        <v>51.1</v>
+        <v>37.8</v>
       </c>
       <c r="R118" t="n">
-        <v>38.7</v>
+        <v>27.6</v>
       </c>
       <c r="S118" t="n">
-        <v>59.8</v>
+        <v>71.7</v>
       </c>
       <c r="T118" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U118" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="V118" t="inlineStr">
         <is>
@@ -32343,7 +32343,7 @@
       </c>
       <c r="X118" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y118" t="inlineStr">
@@ -32385,27 +32385,27 @@
       </c>
       <c r="AH118" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AI118" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="AJ118" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AI118" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AJ118" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AK118" t="inlineStr">
         <is>
-          <t>Last 7 games: 0/14, 0 HR</t>
+          <t>Last 7 games: 9/30, 0 HR</t>
         </is>
       </c>
       <c r="AL118" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 8.9% barrel, 18.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.3% barrel, 11.9 HR allowed</t>
         </is>
       </c>
       <c r="AM118" t="inlineStr">
@@ -32415,104 +32415,104 @@
       </c>
       <c r="AN118" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="AO118" t="inlineStr">
         <is>
-          <t>23.39</t>
+          <t>36.7</t>
         </is>
       </c>
       <c r="AP118" t="inlineStr">
         <is>
-          <t>85.67</t>
+          <t>86.91</t>
         </is>
       </c>
       <c r="AQ118" t="inlineStr">
         <is>
-          <t>95.3063</t>
+          <t>98.3176</t>
         </is>
       </c>
       <c r="AR118" t="inlineStr">
         <is>
-          <t>0.2663</t>
+          <t>0.3834</t>
         </is>
       </c>
       <c r="AS118" t="inlineStr">
         <is>
-          <t>0.0759</t>
+          <t>0.1084</t>
         </is>
       </c>
       <c r="AT118" t="inlineStr">
         <is>
-          <t>0.2491</t>
+          <t>0.3134</t>
         </is>
       </c>
       <c r="AU118" t="inlineStr">
         <is>
-          <t>68.42</t>
+          <t>70.64</t>
         </is>
       </c>
       <c r="AV118" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>12.8</t>
         </is>
       </c>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>36.79</t>
+          <t>38.27</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>29.05</t>
+          <t>20.77</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="AZ118" t="inlineStr">
         <is>
-          <t>0.078</t>
+          <t>0.0957</t>
         </is>
       </c>
       <c r="BA118" t="inlineStr">
         <is>
-          <t>8.94</t>
+          <t>7.32</t>
         </is>
       </c>
       <c r="BB118" t="inlineStr">
         <is>
-          <t>44.1</t>
+          <t>41.61</t>
         </is>
       </c>
       <c r="BC118" t="inlineStr">
         <is>
-          <t>90.42</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="BD118" t="inlineStr">
         <is>
-          <t>0.4664</t>
+          <t>0.3962</t>
         </is>
       </c>
       <c r="BE118" t="inlineStr">
         <is>
-          <t>0.1826</t>
+          <t>0.1472</t>
         </is>
       </c>
       <c r="BF118" t="inlineStr">
         <is>
-          <t>25.59</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="BG118" t="inlineStr"/>
       <c r="BH118" t="inlineStr"/>
       <c r="BI118" t="inlineStr">
         <is>
-          <t>Coors Field</t>
+          <t>American Family Field</t>
         </is>
       </c>
       <c r="BJ118" t="inlineStr"/>
@@ -32523,27 +32523,27 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>693304</t>
+          <t>665804</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Nick Gonzales</t>
+          <t>Miguel Amaya</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-08-03T23:40:00Z</t>
+          <t>2026-08-04T00:05:00Z</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -32553,26 +32553,14 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>Brandon Sproat</t>
-        </is>
-      </c>
-      <c r="J119" t="inlineStr">
-        <is>
-          <t>687075</t>
-        </is>
-      </c>
-      <c r="K119" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
+      <c r="J119" t="inlineStr"/>
+      <c r="K119" t="inlineStr"/>
       <c r="L119" t="n">
-        <v>34.6</v>
+        <v>34</v>
       </c>
       <c r="M119" t="inlineStr">
         <is>
@@ -32590,19 +32578,19 @@
         </is>
       </c>
       <c r="P119" t="n">
-        <v>16.6</v>
+        <v>22</v>
       </c>
       <c r="Q119" t="n">
-        <v>37.8</v>
+        <v>41.2</v>
       </c>
       <c r="R119" t="n">
-        <v>27.6</v>
+        <v>29.8</v>
       </c>
       <c r="S119" t="n">
-        <v>71.7</v>
+        <v>40.2</v>
       </c>
       <c r="T119" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="U119" t="n">
         <v>27</v>
@@ -32619,7 +32607,7 @@
       </c>
       <c r="X119" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y119" t="inlineStr">
@@ -32644,7 +32632,7 @@
       </c>
       <c r="AC119" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:</t>
         </is>
       </c>
       <c r="AD119" t="inlineStr"/>
@@ -32661,12 +32649,12 @@
       </c>
       <c r="AH119" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI119" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ119" t="inlineStr">
@@ -32676,12 +32664,12 @@
       </c>
       <c r="AK119" t="inlineStr">
         <is>
-          <t>Last 7 games: 9/30, 0 HR</t>
+          <t>Last 7 games: 6/20, 0 HR</t>
         </is>
       </c>
       <c r="AL119" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.3% barrel, 11.9 HR allowed</t>
+          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM119" t="inlineStr">
@@ -32691,104 +32679,80 @@
       </c>
       <c r="AN119" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>6.39</t>
         </is>
       </c>
       <c r="AO119" t="inlineStr">
         <is>
-          <t>36.7</t>
+          <t>33.81</t>
         </is>
       </c>
       <c r="AP119" t="inlineStr">
         <is>
-          <t>86.91</t>
+          <t>87.03</t>
         </is>
       </c>
       <c r="AQ119" t="inlineStr">
         <is>
-          <t>98.3176</t>
+          <t>97.668</t>
         </is>
       </c>
       <c r="AR119" t="inlineStr">
         <is>
-          <t>0.3834</t>
+          <t>0.3412</t>
         </is>
       </c>
       <c r="AS119" t="inlineStr">
         <is>
-          <t>0.1084</t>
+          <t>0.1224</t>
         </is>
       </c>
       <c r="AT119" t="inlineStr">
         <is>
-          <t>0.3134</t>
+          <t>0.295</t>
         </is>
       </c>
       <c r="AU119" t="inlineStr">
         <is>
-          <t>70.64</t>
+          <t>70.87</t>
         </is>
       </c>
       <c r="AV119" t="inlineStr">
         <is>
-          <t>12.8</t>
+          <t>13.45</t>
         </is>
       </c>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>38.27</t>
+          <t>39.96</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>20.77</t>
+          <t>31.53</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="AZ119" t="inlineStr">
         <is>
-          <t>0.0957</t>
-        </is>
-      </c>
-      <c r="BA119" t="inlineStr">
-        <is>
-          <t>7.32</t>
-        </is>
-      </c>
-      <c r="BB119" t="inlineStr">
-        <is>
-          <t>41.61</t>
-        </is>
-      </c>
-      <c r="BC119" t="inlineStr">
-        <is>
-          <t>89.3</t>
-        </is>
-      </c>
-      <c r="BD119" t="inlineStr">
-        <is>
-          <t>0.3962</t>
-        </is>
-      </c>
-      <c r="BE119" t="inlineStr">
-        <is>
-          <t>0.1472</t>
-        </is>
-      </c>
-      <c r="BF119" t="inlineStr">
-        <is>
-          <t>22.9</t>
-        </is>
-      </c>
+          <t>0.1469</t>
+        </is>
+      </c>
+      <c r="BA119" t="inlineStr"/>
+      <c r="BB119" t="inlineStr"/>
+      <c r="BC119" t="inlineStr"/>
+      <c r="BD119" t="inlineStr"/>
+      <c r="BE119" t="inlineStr"/>
+      <c r="BF119" t="inlineStr"/>
       <c r="BG119" t="inlineStr"/>
       <c r="BH119" t="inlineStr"/>
       <c r="BI119" t="inlineStr">
         <is>
-          <t>American Family Field</t>
+          <t>Wrigley Field</t>
         </is>
       </c>
       <c r="BJ119" t="inlineStr"/>
@@ -32799,27 +32763,27 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>665804</t>
+          <t>669134</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Miguel Amaya</t>
+          <t>Luis Campusano</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-08-04T00:05:00Z</t>
+          <t>2026-08-04T01:40:00Z</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
@@ -32832,9 +32796,21 @@
           <t>9</t>
         </is>
       </c>
-      <c r="I120" t="inlineStr"/>
-      <c r="J120" t="inlineStr"/>
-      <c r="K120" t="inlineStr"/>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>Brandon Pfaadt</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>694297</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L120" t="n">
         <v>34</v>
       </c>
@@ -32854,22 +32830,22 @@
         </is>
       </c>
       <c r="P120" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Q120" t="n">
-        <v>41.2</v>
+        <v>45.9</v>
       </c>
       <c r="R120" t="n">
-        <v>29.8</v>
+        <v>28.2</v>
       </c>
       <c r="S120" t="n">
         <v>40.2</v>
       </c>
       <c r="T120" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="U120" t="n">
-        <v>27</v>
+        <v>34.2</v>
       </c>
       <c r="V120" t="inlineStr">
         <is>
@@ -32908,7 +32884,7 @@
       </c>
       <c r="AC120" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD120" t="inlineStr"/>
@@ -32925,12 +32901,12 @@
       </c>
       <c r="AH120" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI120" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ120" t="inlineStr">
@@ -32940,12 +32916,12 @@
       </c>
       <c r="AK120" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/20, 0 HR</t>
+          <t>Contact streak: 8/23 over last 7 games</t>
         </is>
       </c>
       <c r="AL120" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 9.6% barrel, 13.4 HR allowed</t>
         </is>
       </c>
       <c r="AM120" t="inlineStr">
@@ -32955,80 +32931,104 @@
       </c>
       <c r="AN120" t="inlineStr">
         <is>
-          <t>6.39</t>
+          <t>5.67</t>
         </is>
       </c>
       <c r="AO120" t="inlineStr">
         <is>
-          <t>33.81</t>
+          <t>40.22</t>
         </is>
       </c>
       <c r="AP120" t="inlineStr">
         <is>
-          <t>87.03</t>
+          <t>87.8</t>
         </is>
       </c>
       <c r="AQ120" t="inlineStr">
         <is>
-          <t>97.668</t>
+          <t>99.3149</t>
         </is>
       </c>
       <c r="AR120" t="inlineStr">
         <is>
-          <t>0.3412</t>
+          <t>0.3088</t>
         </is>
       </c>
       <c r="AS120" t="inlineStr">
         <is>
-          <t>0.1224</t>
+          <t>0.1057</t>
         </is>
       </c>
       <c r="AT120" t="inlineStr">
         <is>
-          <t>0.295</t>
+          <t>0.3025</t>
         </is>
       </c>
       <c r="AU120" t="inlineStr">
         <is>
-          <t>70.87</t>
+          <t>72.4</t>
         </is>
       </c>
       <c r="AV120" t="inlineStr">
         <is>
-          <t>13.45</t>
+          <t>24.95</t>
         </is>
       </c>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>39.96</t>
+          <t>47.33</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>31.53</t>
+          <t>18.12</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="AZ120" t="inlineStr">
         <is>
-          <t>0.1469</t>
-        </is>
-      </c>
-      <c r="BA120" t="inlineStr"/>
-      <c r="BB120" t="inlineStr"/>
-      <c r="BC120" t="inlineStr"/>
-      <c r="BD120" t="inlineStr"/>
-      <c r="BE120" t="inlineStr"/>
-      <c r="BF120" t="inlineStr"/>
+          <t>0.1372</t>
+        </is>
+      </c>
+      <c r="BA120" t="inlineStr">
+        <is>
+          <t>9.57</t>
+        </is>
+      </c>
+      <c r="BB120" t="inlineStr">
+        <is>
+          <t>39.78</t>
+        </is>
+      </c>
+      <c r="BC120" t="inlineStr">
+        <is>
+          <t>89.4</t>
+        </is>
+      </c>
+      <c r="BD120" t="inlineStr">
+        <is>
+          <t>0.4275</t>
+        </is>
+      </c>
+      <c r="BE120" t="inlineStr">
+        <is>
+          <t>0.1715</t>
+        </is>
+      </c>
+      <c r="BF120" t="inlineStr">
+        <is>
+          <t>21.8</t>
+        </is>
+      </c>
       <c r="BG120" t="inlineStr"/>
       <c r="BH120" t="inlineStr"/>
       <c r="BI120" t="inlineStr">
         <is>
-          <t>Wrigley Field</t>
+          <t>Chase Field</t>
         </is>
       </c>
       <c r="BJ120" t="inlineStr"/>
@@ -33039,27 +33039,27 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>669134</t>
+          <t>678391</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Luis Campusano</t>
+          <t>Jorbit Vivas</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-08-04T01:40:00Z</t>
+          <t>2026-08-03T22:40:00Z</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
@@ -33069,17 +33069,17 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>Brandon Pfaadt</t>
+          <t>Aaron Nola</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>694297</t>
+          <t>605400</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
@@ -33088,7 +33088,7 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>34</v>
+        <v>33.7</v>
       </c>
       <c r="M121" t="inlineStr">
         <is>
@@ -33102,26 +33102,26 @@
       </c>
       <c r="O121" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P121" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="Q121" t="n">
-        <v>45.9</v>
+        <v>50.7</v>
       </c>
       <c r="R121" t="n">
-        <v>28.2</v>
+        <v>34.3</v>
       </c>
       <c r="S121" t="n">
-        <v>40.2</v>
+        <v>47.9</v>
       </c>
       <c r="T121" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U121" t="n">
-        <v>34.2</v>
+        <v>10.1</v>
       </c>
       <c r="V121" t="inlineStr">
         <is>
@@ -33135,7 +33135,7 @@
       </c>
       <c r="X121" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y121" t="inlineStr">
@@ -33177,12 +33177,12 @@
       </c>
       <c r="AH121" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI121" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AJ121" t="inlineStr">
@@ -33192,12 +33192,12 @@
       </c>
       <c r="AK121" t="inlineStr">
         <is>
-          <t>Contact streak: 8/23 over last 7 games</t>
+          <t>Last 7 games: 3/16, 0 HR</t>
         </is>
       </c>
       <c r="AL121" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 9.6% barrel, 13.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.9% barrel, 23.6 HR allowed</t>
         </is>
       </c>
       <c r="AM121" t="inlineStr">
@@ -33207,82 +33207,82 @@
       </c>
       <c r="AN121" t="inlineStr">
         <is>
-          <t>5.67</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="AO121" t="inlineStr">
         <is>
-          <t>40.22</t>
+          <t>28.73</t>
         </is>
       </c>
       <c r="AP121" t="inlineStr">
         <is>
-          <t>87.8</t>
+          <t>84.01</t>
         </is>
       </c>
       <c r="AQ121" t="inlineStr">
         <is>
-          <t>99.3149</t>
+          <t>95.6367</t>
         </is>
       </c>
       <c r="AR121" t="inlineStr">
         <is>
-          <t>0.3088</t>
+          <t>0.3275</t>
         </is>
       </c>
       <c r="AS121" t="inlineStr">
         <is>
-          <t>0.1057</t>
+          <t>0.0813</t>
         </is>
       </c>
       <c r="AT121" t="inlineStr">
         <is>
-          <t>0.3025</t>
+          <t>0.2996</t>
         </is>
       </c>
       <c r="AU121" t="inlineStr">
         <is>
-          <t>72.4</t>
+          <t>69.53</t>
         </is>
       </c>
       <c r="AV121" t="inlineStr">
         <is>
-          <t>24.95</t>
+          <t>3.68</t>
         </is>
       </c>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>47.33</t>
+          <t>43.56</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>18.12</t>
+          <t>21.46</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="AZ121" t="inlineStr">
         <is>
-          <t>0.1372</t>
+          <t>0.0925</t>
         </is>
       </c>
       <c r="BA121" t="inlineStr">
         <is>
-          <t>9.57</t>
+          <t>9.87</t>
         </is>
       </c>
       <c r="BB121" t="inlineStr">
         <is>
-          <t>39.78</t>
+          <t>41.83</t>
         </is>
       </c>
       <c r="BC121" t="inlineStr">
         <is>
-          <t>89.4</t>
+          <t>88.84</t>
         </is>
       </c>
       <c r="BD121" t="inlineStr">
@@ -33292,19 +33292,19 @@
       </c>
       <c r="BE121" t="inlineStr">
         <is>
-          <t>0.1715</t>
+          <t>0.1794</t>
         </is>
       </c>
       <c r="BF121" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>27.53</t>
         </is>
       </c>
       <c r="BG121" t="inlineStr"/>
       <c r="BH121" t="inlineStr"/>
       <c r="BI121" t="inlineStr">
         <is>
-          <t>Chase Field</t>
+          <t>Citizens Bank Park</t>
         </is>
       </c>
       <c r="BJ121" t="inlineStr"/>
@@ -33315,27 +33315,27 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>678391</t>
+          <t>701852</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Jorbit Vivas</t>
+          <t>Drew Cavanaugh</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-08-03T22:40:00Z</t>
+          <t>2026-08-04T00:05:00Z</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
@@ -33345,26 +33345,14 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I122" t="inlineStr">
-        <is>
-          <t>Aaron Nola</t>
-        </is>
-      </c>
-      <c r="J122" t="inlineStr">
-        <is>
-          <t>605400</t>
-        </is>
-      </c>
-      <c r="K122" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr"/>
+      <c r="J122" t="inlineStr"/>
+      <c r="K122" t="inlineStr"/>
       <c r="L122" t="n">
-        <v>33.7</v>
+        <v>32.4</v>
       </c>
       <c r="M122" t="inlineStr">
         <is>
@@ -33378,26 +33366,26 @@
       </c>
       <c r="O122" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P122" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="Q122" t="n">
-        <v>50.7</v>
+        <v>41.2</v>
       </c>
       <c r="R122" t="n">
-        <v>34.3</v>
+        <v>27.6</v>
       </c>
       <c r="S122" t="n">
-        <v>47.9</v>
+        <v>71.7</v>
       </c>
       <c r="T122" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="U122" t="n">
-        <v>10.1</v>
+        <v>14.1</v>
       </c>
       <c r="V122" t="inlineStr">
         <is>
@@ -33411,7 +33399,7 @@
       </c>
       <c r="X122" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y122" t="inlineStr">
@@ -33436,7 +33424,7 @@
       </c>
       <c r="AC122" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:</t>
         </is>
       </c>
       <c r="AD122" t="inlineStr"/>
@@ -33458,7 +33446,7 @@
       </c>
       <c r="AI122" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AJ122" t="inlineStr">
@@ -33468,12 +33456,12 @@
       </c>
       <c r="AK122" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/16, 0 HR</t>
+          <t>Last 7 games: 3/14, 0 HR</t>
         </is>
       </c>
       <c r="AL122" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.9% barrel, 23.6 HR allowed</t>
+          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM122" t="inlineStr">
@@ -33483,104 +33471,80 @@
       </c>
       <c r="AN122" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>5.3</t>
         </is>
       </c>
       <c r="AO122" t="inlineStr">
         <is>
-          <t>28.73</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AP122" t="inlineStr">
         <is>
-          <t>84.01</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AQ122" t="inlineStr">
         <is>
-          <t>95.6367</t>
+          <t>96.8228</t>
         </is>
       </c>
       <c r="AR122" t="inlineStr">
         <is>
-          <t>0.3275</t>
+          <t>0.311</t>
         </is>
       </c>
       <c r="AS122" t="inlineStr">
         <is>
-          <t>0.0813</t>
+          <t>0.093</t>
         </is>
       </c>
       <c r="AT122" t="inlineStr">
         <is>
-          <t>0.2996</t>
+          <t>0.308</t>
         </is>
       </c>
       <c r="AU122" t="inlineStr">
         <is>
-          <t>69.53</t>
+          <t>69.4</t>
         </is>
       </c>
       <c r="AV122" t="inlineStr">
         <is>
-          <t>3.68</t>
+          <t>5.3</t>
         </is>
       </c>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>43.56</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>21.46</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ122" t="inlineStr">
         <is>
-          <t>0.0925</t>
-        </is>
-      </c>
-      <c r="BA122" t="inlineStr">
-        <is>
-          <t>9.87</t>
-        </is>
-      </c>
-      <c r="BB122" t="inlineStr">
-        <is>
-          <t>41.83</t>
-        </is>
-      </c>
-      <c r="BC122" t="inlineStr">
-        <is>
-          <t>88.84</t>
-        </is>
-      </c>
-      <c r="BD122" t="inlineStr">
-        <is>
-          <t>0.4275</t>
-        </is>
-      </c>
-      <c r="BE122" t="inlineStr">
-        <is>
-          <t>0.1794</t>
-        </is>
-      </c>
-      <c r="BF122" t="inlineStr">
-        <is>
-          <t>27.53</t>
-        </is>
-      </c>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="BA122" t="inlineStr"/>
+      <c r="BB122" t="inlineStr"/>
+      <c r="BC122" t="inlineStr"/>
+      <c r="BD122" t="inlineStr"/>
+      <c r="BE122" t="inlineStr"/>
+      <c r="BF122" t="inlineStr"/>
       <c r="BG122" t="inlineStr"/>
       <c r="BH122" t="inlineStr"/>
       <c r="BI122" t="inlineStr">
         <is>
-          <t>Citizens Bank Park</t>
+          <t>Globe Life Field</t>
         </is>
       </c>
       <c r="BJ122" t="inlineStr"/>
@@ -33591,24 +33555,24 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>701852</t>
+          <t>677649</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Drew Cavanaugh</t>
+          <t>Ezequiel Duran</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
+          <t>TEX</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
           <t>SF</t>
         </is>
       </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>TEX</t>
-        </is>
-      </c>
       <c r="F123" t="inlineStr">
         <is>
           <t>2026-08-04T00:05:00Z</t>
@@ -33621,14 +33585,26 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr"/>
-      <c r="J123" t="inlineStr"/>
-      <c r="K123" t="inlineStr"/>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>Logan Webb</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>657277</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L123" t="n">
-        <v>32.4</v>
+        <v>32.3</v>
       </c>
       <c r="M123" t="inlineStr">
         <is>
@@ -33646,22 +33622,22 @@
         </is>
       </c>
       <c r="P123" t="n">
-        <v>6.6</v>
+        <v>19.3</v>
       </c>
       <c r="Q123" t="n">
-        <v>41.2</v>
+        <v>30.6</v>
       </c>
       <c r="R123" t="n">
         <v>27.6</v>
       </c>
       <c r="S123" t="n">
-        <v>71.7</v>
+        <v>59.8</v>
       </c>
       <c r="T123" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="U123" t="n">
-        <v>14.1</v>
+        <v>30.3</v>
       </c>
       <c r="V123" t="inlineStr">
         <is>
@@ -33675,7 +33651,7 @@
       </c>
       <c r="X123" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y123" t="inlineStr">
@@ -33700,7 +33676,7 @@
       </c>
       <c r="AC123" t="inlineStr">
         <is>
-          <t>H:2026 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD123" t="inlineStr"/>
@@ -33717,27 +33693,27 @@
       </c>
       <c r="AH123" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI123" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/14, 0 HR</t>
+          <t>Last 7 games: 5/25, 1 HR</t>
         </is>
       </c>
       <c r="AL123" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.4% barrel, 10.5 HR allowed</t>
         </is>
       </c>
       <c r="AM123" t="inlineStr">
@@ -33747,75 +33723,99 @@
       </c>
       <c r="AN123" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>5.26</t>
         </is>
       </c>
       <c r="AO123" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>33.98</t>
         </is>
       </c>
       <c r="AP123" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>87.54</t>
         </is>
       </c>
       <c r="AQ123" t="inlineStr">
         <is>
-          <t>96.8228</t>
+          <t>98.5554</t>
         </is>
       </c>
       <c r="AR123" t="inlineStr">
         <is>
-          <t>0.311</t>
+          <t>0.3531</t>
         </is>
       </c>
       <c r="AS123" t="inlineStr">
         <is>
-          <t>0.093</t>
+          <t>0.1132</t>
         </is>
       </c>
       <c r="AT123" t="inlineStr">
         <is>
-          <t>0.308</t>
+          <t>0.2862</t>
         </is>
       </c>
       <c r="AU123" t="inlineStr">
         <is>
-          <t>69.4</t>
+          <t>72.27</t>
         </is>
       </c>
       <c r="AV123" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>23.89</t>
         </is>
       </c>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>34.75</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>20.95</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="AZ123" t="inlineStr">
         <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="BA123" t="inlineStr"/>
-      <c r="BB123" t="inlineStr"/>
-      <c r="BC123" t="inlineStr"/>
-      <c r="BD123" t="inlineStr"/>
-      <c r="BE123" t="inlineStr"/>
-      <c r="BF123" t="inlineStr"/>
+          <t>0.1411</t>
+        </is>
+      </c>
+      <c r="BA123" t="inlineStr">
+        <is>
+          <t>6.41</t>
+        </is>
+      </c>
+      <c r="BB123" t="inlineStr">
+        <is>
+          <t>39.57</t>
+        </is>
+      </c>
+      <c r="BC123" t="inlineStr">
+        <is>
+          <t>88.79</t>
+        </is>
+      </c>
+      <c r="BD123" t="inlineStr">
+        <is>
+          <t>0.3826</t>
+        </is>
+      </c>
+      <c r="BE123" t="inlineStr">
+        <is>
+          <t>0.1289</t>
+        </is>
+      </c>
+      <c r="BF123" t="inlineStr">
+        <is>
+          <t>18.65</t>
+        </is>
+      </c>
       <c r="BG123" t="inlineStr"/>
       <c r="BH123" t="inlineStr"/>
       <c r="BI123" t="inlineStr">
@@ -33831,12 +33831,12 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>677649</t>
+          <t>553869</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Ezequiel Duran</t>
+          <t>Elias Diaz</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -33861,7 +33861,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -33898,7 +33898,7 @@
         </is>
       </c>
       <c r="P124" t="n">
-        <v>19.3</v>
+        <v>24</v>
       </c>
       <c r="Q124" t="n">
         <v>30.6</v>
@@ -33907,13 +33907,13 @@
         <v>27.6</v>
       </c>
       <c r="S124" t="n">
-        <v>59.8</v>
+        <v>47.9</v>
       </c>
       <c r="T124" t="n">
         <v>50</v>
       </c>
       <c r="U124" t="n">
-        <v>30.3</v>
+        <v>33.7</v>
       </c>
       <c r="V124" t="inlineStr">
         <is>
@@ -33927,7 +33927,7 @@
       </c>
       <c r="X124" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y124" t="inlineStr">
@@ -33969,12 +33969,12 @@
       </c>
       <c r="AH124" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI124" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AJ124" t="inlineStr">
@@ -33984,7 +33984,7 @@
       </c>
       <c r="AK124" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/25, 1 HR</t>
+          <t>Last 7 games: 4/18, 1 HR</t>
         </is>
       </c>
       <c r="AL124" t="inlineStr">
@@ -33999,67 +33999,67 @@
       </c>
       <c r="AN124" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>5.92</t>
         </is>
       </c>
       <c r="AO124" t="inlineStr">
         <is>
-          <t>33.98</t>
+          <t>36.39</t>
         </is>
       </c>
       <c r="AP124" t="inlineStr">
         <is>
-          <t>87.54</t>
+          <t>86.79</t>
         </is>
       </c>
       <c r="AQ124" t="inlineStr">
         <is>
-          <t>98.5554</t>
+          <t>99.3532</t>
         </is>
       </c>
       <c r="AR124" t="inlineStr">
         <is>
-          <t>0.3531</t>
+          <t>0.3543</t>
         </is>
       </c>
       <c r="AS124" t="inlineStr">
         <is>
-          <t>0.1132</t>
+          <t>0.1264</t>
         </is>
       </c>
       <c r="AT124" t="inlineStr">
         <is>
-          <t>0.2862</t>
+          <t>0.268</t>
         </is>
       </c>
       <c r="AU124" t="inlineStr">
         <is>
-          <t>72.27</t>
+          <t>74.27</t>
         </is>
       </c>
       <c r="AV124" t="inlineStr">
         <is>
-          <t>23.89</t>
+          <t>42.74</t>
         </is>
       </c>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>34.75</t>
+          <t>39.33</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>20.95</t>
+          <t>28.22</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>6.2</t>
         </is>
       </c>
       <c r="AZ124" t="inlineStr">
         <is>
-          <t>0.1411</t>
+          <t>0.1718</t>
         </is>
       </c>
       <c r="BA124" t="inlineStr">
@@ -34107,27 +34107,27 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>553869</t>
+          <t>650333</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Elias Diaz</t>
+          <t>Luis Arraez</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-08-04T00:05:00Z</t>
+          <t>2026-08-03T22:40:00Z</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -34137,26 +34137,26 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>Logan Webb</t>
+          <t>Andrew Alvarez</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>657277</t>
+          <t>674841</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L125" t="n">
-        <v>32.3</v>
+        <v>32.2</v>
       </c>
       <c r="M125" t="inlineStr">
         <is>
@@ -34170,26 +34170,26 @@
       </c>
       <c r="O125" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P125" t="n">
-        <v>24</v>
+        <v>7.1</v>
       </c>
       <c r="Q125" t="n">
-        <v>30.6</v>
+        <v>23</v>
       </c>
       <c r="R125" t="n">
-        <v>27.6</v>
+        <v>34.3</v>
       </c>
       <c r="S125" t="n">
-        <v>47.9</v>
+        <v>95.5</v>
       </c>
       <c r="T125" t="n">
         <v>50</v>
       </c>
       <c r="U125" t="n">
-        <v>33.7</v>
+        <v>27</v>
       </c>
       <c r="V125" t="inlineStr">
         <is>
@@ -34203,7 +34203,7 @@
       </c>
       <c r="X125" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y125" t="inlineStr">
@@ -34245,27 +34245,27 @@
       </c>
       <c r="AH125" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI125" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK125" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/18, 1 HR</t>
+          <t>Last 7 games: 9/30, 0 HR</t>
         </is>
       </c>
       <c r="AL125" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.4% barrel, 10.5 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 4.8% barrel, 1.7 HR allowed</t>
         </is>
       </c>
       <c r="AM125" t="inlineStr">
@@ -34275,104 +34275,104 @@
       </c>
       <c r="AN125" t="inlineStr">
         <is>
-          <t>5.92</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="AO125" t="inlineStr">
         <is>
-          <t>36.39</t>
+          <t>19.22</t>
         </is>
       </c>
       <c r="AP125" t="inlineStr">
         <is>
-          <t>86.79</t>
+          <t>86.73</t>
         </is>
       </c>
       <c r="AQ125" t="inlineStr">
         <is>
-          <t>99.3532</t>
+          <t>94.0255</t>
         </is>
       </c>
       <c r="AR125" t="inlineStr">
         <is>
-          <t>0.3543</t>
+          <t>0.3693</t>
         </is>
       </c>
       <c r="AS125" t="inlineStr">
         <is>
-          <t>0.1264</t>
+          <t>0.083</t>
         </is>
       </c>
       <c r="AT125" t="inlineStr">
         <is>
-          <t>0.268</t>
+          <t>0.3037</t>
         </is>
       </c>
       <c r="AU125" t="inlineStr">
         <is>
-          <t>74.27</t>
+          <t>62.92</t>
         </is>
       </c>
       <c r="AV125" t="inlineStr">
         <is>
-          <t>42.74</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>39.33</t>
+          <t>30.1</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>28.22</t>
+          <t>27.19</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr">
         <is>
-          <t>6.2</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="AZ125" t="inlineStr">
         <is>
-          <t>0.1718</t>
+          <t>0.1112</t>
         </is>
       </c>
       <c r="BA125" t="inlineStr">
         <is>
-          <t>6.41</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="BB125" t="inlineStr">
         <is>
-          <t>39.57</t>
+          <t>41.92</t>
         </is>
       </c>
       <c r="BC125" t="inlineStr">
         <is>
-          <t>88.79</t>
+          <t>89.32</t>
         </is>
       </c>
       <c r="BD125" t="inlineStr">
         <is>
-          <t>0.3826</t>
+          <t>0.3507</t>
         </is>
       </c>
       <c r="BE125" t="inlineStr">
         <is>
-          <t>0.1289</t>
+          <t>0.1053</t>
         </is>
       </c>
       <c r="BF125" t="inlineStr">
         <is>
-          <t>18.65</t>
+          <t>16.01</t>
         </is>
       </c>
       <c r="BG125" t="inlineStr"/>
       <c r="BH125" t="inlineStr"/>
       <c r="BI125" t="inlineStr">
         <is>
-          <t>Globe Life Field</t>
+          <t>Citizens Bank Park</t>
         </is>
       </c>
       <c r="BJ125" t="inlineStr"/>
@@ -34383,27 +34383,27 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>650333</t>
+          <t>665926</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Luis Arraez</t>
+          <t>Andres Gimenez</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2026-08-03T22:40:00Z</t>
+          <t>2026-08-04T00:10:00Z</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -34413,26 +34413,26 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>Andrew Alvarez</t>
+          <t>Cristian Javier</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>674841</t>
+          <t>664299</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L126" t="n">
-        <v>32.2</v>
+        <v>32.1</v>
       </c>
       <c r="M126" t="inlineStr">
         <is>
@@ -34446,26 +34446,26 @@
       </c>
       <c r="O126" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P126" t="n">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="Q126" t="n">
-        <v>23</v>
+        <v>47.1</v>
       </c>
       <c r="R126" t="n">
-        <v>34.3</v>
+        <v>27.6</v>
       </c>
       <c r="S126" t="n">
-        <v>95.5</v>
+        <v>40.2</v>
       </c>
       <c r="T126" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U126" t="n">
-        <v>27</v>
+        <v>29.4</v>
       </c>
       <c r="V126" t="inlineStr">
         <is>
@@ -34479,7 +34479,7 @@
       </c>
       <c r="X126" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y126" t="inlineStr">
@@ -34521,12 +34521,12 @@
       </c>
       <c r="AH126" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI126" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ126" t="inlineStr">
@@ -34536,119 +34536,119 @@
       </c>
       <c r="AK126" t="inlineStr">
         <is>
-          <t>Last 7 games: 9/30, 0 HR</t>
+          <t>Last 7 games: 6/19, 0 HR</t>
         </is>
       </c>
       <c r="AL126" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 4.8% barrel, 1.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.7% barrel, 3.0 HR allowed</t>
         </is>
       </c>
       <c r="AM126" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN126" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>3.56</t>
         </is>
       </c>
       <c r="AO126" t="inlineStr">
         <is>
-          <t>19.22</t>
+          <t>24.62</t>
         </is>
       </c>
       <c r="AP126" t="inlineStr">
         <is>
-          <t>86.73</t>
+          <t>85.95</t>
         </is>
       </c>
       <c r="AQ126" t="inlineStr">
         <is>
-          <t>94.0255</t>
+          <t>95.8276</t>
         </is>
       </c>
       <c r="AR126" t="inlineStr">
         <is>
-          <t>0.3693</t>
+          <t>0.3337</t>
         </is>
       </c>
       <c r="AS126" t="inlineStr">
         <is>
-          <t>0.083</t>
+          <t>0.0957</t>
         </is>
       </c>
       <c r="AT126" t="inlineStr">
         <is>
-          <t>0.3037</t>
+          <t>0.2807</t>
         </is>
       </c>
       <c r="AU126" t="inlineStr">
         <is>
-          <t>62.92</t>
+          <t>68.39</t>
         </is>
       </c>
       <c r="AV126" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>4.93</t>
         </is>
       </c>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>30.1</t>
+          <t>37.89</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>27.19</t>
+          <t>22.39</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="AZ126" t="inlineStr">
         <is>
-          <t>0.1112</t>
+          <t>0.1149</t>
         </is>
       </c>
       <c r="BA126" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>9.72</t>
         </is>
       </c>
       <c r="BB126" t="inlineStr">
         <is>
-          <t>41.92</t>
+          <t>39.28</t>
         </is>
       </c>
       <c r="BC126" t="inlineStr">
         <is>
-          <t>89.32</t>
+          <t>90.3</t>
         </is>
       </c>
       <c r="BD126" t="inlineStr">
         <is>
-          <t>0.3507</t>
+          <t>0.3998</t>
         </is>
       </c>
       <c r="BE126" t="inlineStr">
         <is>
-          <t>0.1053</t>
+          <t>0.1565</t>
         </is>
       </c>
       <c r="BF126" t="inlineStr">
         <is>
-          <t>16.01</t>
+          <t>38.45</t>
         </is>
       </c>
       <c r="BG126" t="inlineStr"/>
       <c r="BH126" t="inlineStr"/>
       <c r="BI126" t="inlineStr">
         <is>
-          <t>Citizens Bank Park</t>
+          <t>Daikin Park</t>
         </is>
       </c>
       <c r="BJ126" t="inlineStr"/>
@@ -34659,27 +34659,27 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>665926</t>
+          <t>687551</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Andres Gimenez</t>
+          <t>Drew Gilbert</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2026-08-04T00:10:00Z</t>
+          <t>2026-08-04T00:05:00Z</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
@@ -34689,26 +34689,14 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr">
-        <is>
-          <t>Cristian Javier</t>
-        </is>
-      </c>
-      <c r="J127" t="inlineStr">
-        <is>
-          <t>664299</t>
-        </is>
-      </c>
-      <c r="K127" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr"/>
+      <c r="J127" t="inlineStr"/>
+      <c r="K127" t="inlineStr"/>
       <c r="L127" t="n">
-        <v>32.1</v>
+        <v>32</v>
       </c>
       <c r="M127" t="inlineStr">
         <is>
@@ -34722,26 +34710,26 @@
       </c>
       <c r="O127" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P127" t="n">
-        <v>7.2</v>
+        <v>13.3</v>
       </c>
       <c r="Q127" t="n">
-        <v>47.1</v>
+        <v>41.2</v>
       </c>
       <c r="R127" t="n">
         <v>27.6</v>
       </c>
       <c r="S127" t="n">
-        <v>40.2</v>
+        <v>47.9</v>
       </c>
       <c r="T127" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="U127" t="n">
-        <v>29.4</v>
+        <v>28.9</v>
       </c>
       <c r="V127" t="inlineStr">
         <is>
@@ -34755,7 +34743,7 @@
       </c>
       <c r="X127" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y127" t="inlineStr">
@@ -34780,7 +34768,7 @@
       </c>
       <c r="AC127" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:</t>
         </is>
       </c>
       <c r="AD127" t="inlineStr"/>
@@ -34797,12 +34785,12 @@
       </c>
       <c r="AH127" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI127" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AJ127" t="inlineStr">
@@ -34812,119 +34800,95 @@
       </c>
       <c r="AK127" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/19, 0 HR</t>
+          <t>Last 7 games: 5/16, 0 HR</t>
         </is>
       </c>
       <c r="AL127" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.7% barrel, 3.0 HR allowed</t>
+          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM127" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN127" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="AO127" t="inlineStr">
         <is>
-          <t>24.62</t>
+          <t>34.82</t>
         </is>
       </c>
       <c r="AP127" t="inlineStr">
         <is>
-          <t>85.95</t>
+          <t>86.25</t>
         </is>
       </c>
       <c r="AQ127" t="inlineStr">
         <is>
-          <t>95.8276</t>
+          <t>97.7864</t>
         </is>
       </c>
       <c r="AR127" t="inlineStr">
         <is>
-          <t>0.3337</t>
+          <t>0.3479</t>
         </is>
       </c>
       <c r="AS127" t="inlineStr">
         <is>
-          <t>0.0957</t>
+          <t>0.1041</t>
         </is>
       </c>
       <c r="AT127" t="inlineStr">
         <is>
-          <t>0.2807</t>
+          <t>0.2973</t>
         </is>
       </c>
       <c r="AU127" t="inlineStr">
         <is>
-          <t>68.39</t>
+          <t>70.52</t>
         </is>
       </c>
       <c r="AV127" t="inlineStr">
         <is>
-          <t>4.93</t>
+          <t>9.92</t>
         </is>
       </c>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>37.89</t>
+          <t>40.49</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>22.39</t>
+          <t>18.36</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="AZ127" t="inlineStr">
         <is>
-          <t>0.1149</t>
-        </is>
-      </c>
-      <c r="BA127" t="inlineStr">
-        <is>
-          <t>9.72</t>
-        </is>
-      </c>
-      <c r="BB127" t="inlineStr">
-        <is>
-          <t>39.28</t>
-        </is>
-      </c>
-      <c r="BC127" t="inlineStr">
-        <is>
-          <t>90.3</t>
-        </is>
-      </c>
-      <c r="BD127" t="inlineStr">
-        <is>
-          <t>0.3998</t>
-        </is>
-      </c>
-      <c r="BE127" t="inlineStr">
-        <is>
-          <t>0.1565</t>
-        </is>
-      </c>
-      <c r="BF127" t="inlineStr">
-        <is>
-          <t>38.45</t>
-        </is>
-      </c>
+          <t>0.1285</t>
+        </is>
+      </c>
+      <c r="BA127" t="inlineStr"/>
+      <c r="BB127" t="inlineStr"/>
+      <c r="BC127" t="inlineStr"/>
+      <c r="BD127" t="inlineStr"/>
+      <c r="BE127" t="inlineStr"/>
+      <c r="BF127" t="inlineStr"/>
       <c r="BG127" t="inlineStr"/>
       <c r="BH127" t="inlineStr"/>
       <c r="BI127" t="inlineStr">
         <is>
-          <t>Daikin Park</t>
+          <t>Globe Life Field</t>
         </is>
       </c>
       <c r="BJ127" t="inlineStr"/>
@@ -34935,27 +34899,27 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>687551</t>
+          <t>683083</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Drew Gilbert</t>
+          <t>Nasim Nunez</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>2026-08-04T00:05:00Z</t>
+          <t>2026-08-03T22:40:00Z</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
@@ -34965,14 +34929,26 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr"/>
-      <c r="J128" t="inlineStr"/>
-      <c r="K128" t="inlineStr"/>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>Aaron Nola</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>605400</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L128" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="M128" t="inlineStr">
         <is>
@@ -34986,26 +34962,26 @@
       </c>
       <c r="O128" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P128" t="n">
-        <v>13.3</v>
+        <v>5</v>
       </c>
       <c r="Q128" t="n">
-        <v>41.2</v>
+        <v>49</v>
       </c>
       <c r="R128" t="n">
-        <v>27.6</v>
+        <v>34.3</v>
       </c>
       <c r="S128" t="n">
-        <v>47.9</v>
+        <v>40.2</v>
       </c>
       <c r="T128" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="U128" t="n">
-        <v>28.9</v>
+        <v>0.8</v>
       </c>
       <c r="V128" t="inlineStr">
         <is>
@@ -35019,7 +34995,7 @@
       </c>
       <c r="X128" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y128" t="inlineStr">
@@ -35044,7 +35020,7 @@
       </c>
       <c r="AC128" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD128" t="inlineStr"/>
@@ -35061,12 +35037,12 @@
       </c>
       <c r="AH128" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI128" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ128" t="inlineStr">
@@ -35076,12 +35052,12 @@
       </c>
       <c r="AK128" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/16, 0 HR</t>
+          <t>Last 7 games: 3/24, 0 HR</t>
         </is>
       </c>
       <c r="AL128" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 9.9% barrel, 23.6 HR allowed</t>
         </is>
       </c>
       <c r="AM128" t="inlineStr">
@@ -35091,80 +35067,104 @@
       </c>
       <c r="AN128" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="AO128" t="inlineStr">
         <is>
-          <t>34.82</t>
+          <t>27.57</t>
         </is>
       </c>
       <c r="AP128" t="inlineStr">
         <is>
-          <t>86.25</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AQ128" t="inlineStr">
         <is>
-          <t>97.7864</t>
+          <t>95.8969</t>
         </is>
       </c>
       <c r="AR128" t="inlineStr">
         <is>
-          <t>0.3479</t>
+          <t>0.3033</t>
         </is>
       </c>
       <c r="AS128" t="inlineStr">
         <is>
-          <t>0.1041</t>
+          <t>0.0734</t>
         </is>
       </c>
       <c r="AT128" t="inlineStr">
         <is>
-          <t>0.2973</t>
+          <t>0.2792</t>
         </is>
       </c>
       <c r="AU128" t="inlineStr">
         <is>
-          <t>70.52</t>
+          <t>68.74</t>
         </is>
       </c>
       <c r="AV128" t="inlineStr">
         <is>
-          <t>9.92</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>40.49</t>
+          <t>32.69</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>18.36</t>
+          <t>18.12</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="AZ128" t="inlineStr">
         <is>
-          <t>0.1285</t>
-        </is>
-      </c>
-      <c r="BA128" t="inlineStr"/>
-      <c r="BB128" t="inlineStr"/>
-      <c r="BC128" t="inlineStr"/>
-      <c r="BD128" t="inlineStr"/>
-      <c r="BE128" t="inlineStr"/>
-      <c r="BF128" t="inlineStr"/>
+          <t>0.0797</t>
+        </is>
+      </c>
+      <c r="BA128" t="inlineStr">
+        <is>
+          <t>9.87</t>
+        </is>
+      </c>
+      <c r="BB128" t="inlineStr">
+        <is>
+          <t>41.83</t>
+        </is>
+      </c>
+      <c r="BC128" t="inlineStr">
+        <is>
+          <t>88.84</t>
+        </is>
+      </c>
+      <c r="BD128" t="inlineStr">
+        <is>
+          <t>0.4275</t>
+        </is>
+      </c>
+      <c r="BE128" t="inlineStr">
+        <is>
+          <t>0.1794</t>
+        </is>
+      </c>
+      <c r="BF128" t="inlineStr">
+        <is>
+          <t>27.53</t>
+        </is>
+      </c>
       <c r="BG128" t="inlineStr"/>
       <c r="BH128" t="inlineStr"/>
       <c r="BI128" t="inlineStr">
         <is>
-          <t>Globe Life Field</t>
+          <t>Citizens Bank Park</t>
         </is>
       </c>
       <c r="BJ128" t="inlineStr"/>
@@ -35175,27 +35175,27 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>683083</t>
+          <t>806198</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Nasim Nunez</t>
+          <t>Cooper Pratt</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-08-03T22:40:00Z</t>
+          <t>2026-08-03T23:40:00Z</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
@@ -35205,17 +35205,17 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>Aaron Nola</t>
+          <t>Bubba Chandler</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>605400</t>
+          <t>696149</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
@@ -35224,7 +35224,7 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>31</v>
+        <v>30.7</v>
       </c>
       <c r="M129" t="inlineStr">
         <is>
@@ -35238,26 +35238,26 @@
       </c>
       <c r="O129" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P129" t="n">
-        <v>5</v>
+        <v>16.1</v>
       </c>
       <c r="Q129" t="n">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="R129" t="n">
-        <v>34.3</v>
+        <v>27.6</v>
       </c>
       <c r="S129" t="n">
-        <v>40.2</v>
+        <v>47.9</v>
       </c>
       <c r="T129" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U129" t="n">
-        <v>0.8</v>
+        <v>32</v>
       </c>
       <c r="V129" t="inlineStr">
         <is>
@@ -35271,7 +35271,7 @@
       </c>
       <c r="X129" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y129" t="inlineStr">
@@ -35296,7 +35296,7 @@
       </c>
       <c r="AC129" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD129" t="inlineStr"/>
@@ -35313,12 +35313,12 @@
       </c>
       <c r="AH129" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI129" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ129" t="inlineStr">
@@ -35328,12 +35328,12 @@
       </c>
       <c r="AK129" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/24, 0 HR</t>
+          <t>Contact streak: 7/21 over last 7 games</t>
         </is>
       </c>
       <c r="AL129" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 9.9% barrel, 23.6 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.2% barrel, 7.6 HR allowed</t>
         </is>
       </c>
       <c r="AM129" t="inlineStr">
@@ -35343,104 +35343,104 @@
       </c>
       <c r="AN129" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="AO129" t="inlineStr">
         <is>
-          <t>27.57</t>
+          <t>30.9</t>
         </is>
       </c>
       <c r="AP129" t="inlineStr">
         <is>
-          <t>85.8</t>
+          <t>87.9</t>
         </is>
       </c>
       <c r="AQ129" t="inlineStr">
         <is>
-          <t>95.8969</t>
+          <t>97.1628</t>
         </is>
       </c>
       <c r="AR129" t="inlineStr">
         <is>
-          <t>0.3033</t>
+          <t>0.376</t>
         </is>
       </c>
       <c r="AS129" t="inlineStr">
         <is>
-          <t>0.0734</t>
+          <t>0.103</t>
         </is>
       </c>
       <c r="AT129" t="inlineStr">
         <is>
-          <t>0.2792</t>
+          <t>0.338</t>
         </is>
       </c>
       <c r="AU129" t="inlineStr">
         <is>
-          <t>68.74</t>
+          <t>70.3</t>
         </is>
       </c>
       <c r="AV129" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>32.69</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>18.12</t>
+          <t>22.3</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AZ129" t="inlineStr">
         <is>
-          <t>0.0797</t>
+          <t>0.102</t>
         </is>
       </c>
       <c r="BA129" t="inlineStr">
         <is>
-          <t>9.87</t>
+          <t>7.16</t>
         </is>
       </c>
       <c r="BB129" t="inlineStr">
         <is>
-          <t>41.83</t>
+          <t>37.97</t>
         </is>
       </c>
       <c r="BC129" t="inlineStr">
         <is>
-          <t>88.84</t>
+          <t>89.22</t>
         </is>
       </c>
       <c r="BD129" t="inlineStr">
         <is>
-          <t>0.4275</t>
+          <t>0.3779</t>
         </is>
       </c>
       <c r="BE129" t="inlineStr">
         <is>
-          <t>0.1794</t>
+          <t>0.1532</t>
         </is>
       </c>
       <c r="BF129" t="inlineStr">
         <is>
-          <t>27.53</t>
+          <t>26.93</t>
         </is>
       </c>
       <c r="BG129" t="inlineStr"/>
       <c r="BH129" t="inlineStr"/>
       <c r="BI129" t="inlineStr">
         <is>
-          <t>Citizens Bank Park</t>
+          <t>American Family Field</t>
         </is>
       </c>
       <c r="BJ129" t="inlineStr"/>
@@ -35451,27 +35451,27 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>806198</t>
+          <t>676391</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Cooper Pratt</t>
+          <t>Ernie Clement</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>2026-08-03T23:40:00Z</t>
+          <t>2026-08-04T00:10:00Z</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
@@ -35481,17 +35481,17 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>Bubba Chandler</t>
+          <t>Cristian Javier</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>696149</t>
+          <t>664299</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
@@ -35518,22 +35518,22 @@
         </is>
       </c>
       <c r="P130" t="n">
-        <v>16.1</v>
+        <v>6</v>
       </c>
       <c r="Q130" t="n">
-        <v>35</v>
+        <v>47.1</v>
       </c>
       <c r="R130" t="n">
         <v>27.6</v>
       </c>
       <c r="S130" t="n">
-        <v>47.9</v>
+        <v>59.8</v>
       </c>
       <c r="T130" t="n">
         <v>50</v>
       </c>
       <c r="U130" t="n">
-        <v>32</v>
+        <v>7.9</v>
       </c>
       <c r="V130" t="inlineStr">
         <is>
@@ -35547,7 +35547,7 @@
       </c>
       <c r="X130" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y130" t="inlineStr">
@@ -35572,7 +35572,7 @@
       </c>
       <c r="AC130" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD130" t="inlineStr"/>
@@ -35589,12 +35589,12 @@
       </c>
       <c r="AH130" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI130" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ130" t="inlineStr">
@@ -35604,119 +35604,119 @@
       </c>
       <c r="AK130" t="inlineStr">
         <is>
-          <t>Contact streak: 7/21 over last 7 games</t>
+          <t>Last 7 games: 5/29, 0 HR</t>
         </is>
       </c>
       <c r="AL130" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.2% barrel, 7.6 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 9.7% barrel, 3.0 HR allowed</t>
         </is>
       </c>
       <c r="AM130" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN130" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="AO130" t="inlineStr">
         <is>
-          <t>30.9</t>
+          <t>22.78</t>
         </is>
       </c>
       <c r="AP130" t="inlineStr">
         <is>
-          <t>87.9</t>
+          <t>85.34</t>
         </is>
       </c>
       <c r="AQ130" t="inlineStr">
         <is>
-          <t>97.1628</t>
+          <t>94.8467</t>
         </is>
       </c>
       <c r="AR130" t="inlineStr">
         <is>
-          <t>0.376</t>
+          <t>0.3415</t>
         </is>
       </c>
       <c r="AS130" t="inlineStr">
         <is>
-          <t>0.103</t>
+          <t>0.0881</t>
         </is>
       </c>
       <c r="AT130" t="inlineStr">
         <is>
-          <t>0.338</t>
+          <t>0.275</t>
         </is>
       </c>
       <c r="AU130" t="inlineStr">
         <is>
-          <t>70.3</t>
+          <t>67.46</t>
         </is>
       </c>
       <c r="AV130" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>42.34</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>22.3</t>
+          <t>28.32</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="AZ130" t="inlineStr">
         <is>
-          <t>0.102</t>
+          <t>0.1245</t>
         </is>
       </c>
       <c r="BA130" t="inlineStr">
         <is>
-          <t>7.16</t>
+          <t>9.72</t>
         </is>
       </c>
       <c r="BB130" t="inlineStr">
         <is>
-          <t>37.97</t>
+          <t>39.28</t>
         </is>
       </c>
       <c r="BC130" t="inlineStr">
         <is>
-          <t>89.22</t>
+          <t>90.3</t>
         </is>
       </c>
       <c r="BD130" t="inlineStr">
         <is>
-          <t>0.3779</t>
+          <t>0.3998</t>
         </is>
       </c>
       <c r="BE130" t="inlineStr">
         <is>
-          <t>0.1532</t>
+          <t>0.1565</t>
         </is>
       </c>
       <c r="BF130" t="inlineStr">
         <is>
-          <t>26.93</t>
+          <t>38.45</t>
         </is>
       </c>
       <c r="BG130" t="inlineStr"/>
       <c r="BH130" t="inlineStr"/>
       <c r="BI130" t="inlineStr">
         <is>
-          <t>American Family Field</t>
+          <t>Daikin Park</t>
         </is>
       </c>
       <c r="BJ130" t="inlineStr"/>
@@ -35727,27 +35727,27 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>676391</t>
+          <t>666152</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Ernie Clement</t>
+          <t>David Hamilton</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>2026-08-04T00:10:00Z</t>
+          <t>2026-08-03T23:40:00Z</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
@@ -35757,17 +35757,17 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>Cristian Javier</t>
+          <t>Bubba Chandler</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>664299</t>
+          <t>696149</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
@@ -35776,7 +35776,7 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>30.7</v>
+        <v>30.4</v>
       </c>
       <c r="M131" t="inlineStr">
         <is>
@@ -35790,26 +35790,26 @@
       </c>
       <c r="O131" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P131" t="n">
-        <v>6</v>
+        <v>12.3</v>
       </c>
       <c r="Q131" t="n">
-        <v>47.1</v>
+        <v>35</v>
       </c>
       <c r="R131" t="n">
         <v>27.6</v>
       </c>
       <c r="S131" t="n">
-        <v>59.8</v>
+        <v>40.2</v>
       </c>
       <c r="T131" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U131" t="n">
-        <v>7.9</v>
+        <v>19.5</v>
       </c>
       <c r="V131" t="inlineStr">
         <is>
@@ -35823,7 +35823,7 @@
       </c>
       <c r="X131" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y131" t="inlineStr">
@@ -35870,7 +35870,7 @@
       </c>
       <c r="AI131" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ131" t="inlineStr">
@@ -35880,119 +35880,119 @@
       </c>
       <c r="AK131" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/29, 0 HR</t>
+          <t>Last 7 games: 5/20, 0 HR</t>
         </is>
       </c>
       <c r="AL131" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 9.7% barrel, 3.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.2% barrel, 7.6 HR allowed</t>
         </is>
       </c>
       <c r="AM131" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN131" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>4.6</t>
         </is>
       </c>
       <c r="AO131" t="inlineStr">
         <is>
-          <t>22.78</t>
+          <t>27.66</t>
         </is>
       </c>
       <c r="AP131" t="inlineStr">
         <is>
-          <t>85.34</t>
+          <t>86.88</t>
         </is>
       </c>
       <c r="AQ131" t="inlineStr">
         <is>
-          <t>94.8467</t>
+          <t>96.9916</t>
         </is>
       </c>
       <c r="AR131" t="inlineStr">
         <is>
-          <t>0.3415</t>
+          <t>0.3064</t>
         </is>
       </c>
       <c r="AS131" t="inlineStr">
         <is>
-          <t>0.0881</t>
+          <t>0.0988</t>
         </is>
       </c>
       <c r="AT131" t="inlineStr">
         <is>
-          <t>0.275</t>
+          <t>0.2663</t>
         </is>
       </c>
       <c r="AU131" t="inlineStr">
         <is>
-          <t>67.46</t>
+          <t>69.94</t>
         </is>
       </c>
       <c r="AV131" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>7.57</t>
         </is>
       </c>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>42.34</t>
+          <t>34.76</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>28.32</t>
+          <t>26.72</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>3.9</t>
         </is>
       </c>
       <c r="AZ131" t="inlineStr">
         <is>
-          <t>0.1245</t>
+          <t>0.1042</t>
         </is>
       </c>
       <c r="BA131" t="inlineStr">
         <is>
-          <t>9.72</t>
+          <t>7.16</t>
         </is>
       </c>
       <c r="BB131" t="inlineStr">
         <is>
-          <t>39.28</t>
+          <t>37.97</t>
         </is>
       </c>
       <c r="BC131" t="inlineStr">
         <is>
-          <t>90.3</t>
+          <t>89.22</t>
         </is>
       </c>
       <c r="BD131" t="inlineStr">
         <is>
-          <t>0.3998</t>
+          <t>0.3779</t>
         </is>
       </c>
       <c r="BE131" t="inlineStr">
         <is>
-          <t>0.1565</t>
+          <t>0.1532</t>
         </is>
       </c>
       <c r="BF131" t="inlineStr">
         <is>
-          <t>38.45</t>
+          <t>26.93</t>
         </is>
       </c>
       <c r="BG131" t="inlineStr"/>
       <c r="BH131" t="inlineStr"/>
       <c r="BI131" t="inlineStr">
         <is>
-          <t>Daikin Park</t>
+          <t>American Family Field</t>
         </is>
       </c>
       <c r="BJ131" t="inlineStr"/>
@@ -36003,27 +36003,27 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>666152</t>
+          <t>683766</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>David Hamilton</t>
+          <t>Christian Koss</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>2026-08-03T23:40:00Z</t>
+          <t>2026-08-04T00:05:00Z</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -36033,26 +36033,14 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="I132" t="inlineStr">
-        <is>
-          <t>Bubba Chandler</t>
-        </is>
-      </c>
-      <c r="J132" t="inlineStr">
-        <is>
-          <t>696149</t>
-        </is>
-      </c>
-      <c r="K132" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr"/>
+      <c r="J132" t="inlineStr"/>
+      <c r="K132" t="inlineStr"/>
       <c r="L132" t="n">
-        <v>30.4</v>
+        <v>30.1</v>
       </c>
       <c r="M132" t="inlineStr">
         <is>
@@ -36066,26 +36054,26 @@
       </c>
       <c r="O132" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P132" t="n">
-        <v>12.3</v>
+        <v>5.4</v>
       </c>
       <c r="Q132" t="n">
-        <v>35</v>
+        <v>41.2</v>
       </c>
       <c r="R132" t="n">
         <v>27.6</v>
       </c>
       <c r="S132" t="n">
-        <v>40.2</v>
+        <v>59.8</v>
       </c>
       <c r="T132" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="U132" t="n">
-        <v>19.5</v>
+        <v>10.6</v>
       </c>
       <c r="V132" t="inlineStr">
         <is>
@@ -36099,7 +36087,7 @@
       </c>
       <c r="X132" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y132" t="inlineStr">
@@ -36124,7 +36112,7 @@
       </c>
       <c r="AC132" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:</t>
         </is>
       </c>
       <c r="AD132" t="inlineStr"/>
@@ -36141,12 +36129,12 @@
       </c>
       <c r="AH132" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI132" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ132" t="inlineStr">
@@ -36156,12 +36144,12 @@
       </c>
       <c r="AK132" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/20, 0 HR</t>
+          <t>Last 7 games: 4/21, 0 HR</t>
         </is>
       </c>
       <c r="AL132" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.2% barrel, 7.6 HR allowed</t>
+          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM132" t="inlineStr">
@@ -36171,104 +36159,80 @@
       </c>
       <c r="AN132" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>3.83</t>
         </is>
       </c>
       <c r="AO132" t="inlineStr">
         <is>
-          <t>27.66</t>
+          <t>26.53</t>
         </is>
       </c>
       <c r="AP132" t="inlineStr">
         <is>
-          <t>86.88</t>
+          <t>84.66</t>
         </is>
       </c>
       <c r="AQ132" t="inlineStr">
         <is>
-          <t>96.9916</t>
+          <t>96.0366</t>
         </is>
       </c>
       <c r="AR132" t="inlineStr">
         <is>
-          <t>0.3064</t>
+          <t>0.2732</t>
         </is>
       </c>
       <c r="AS132" t="inlineStr">
         <is>
-          <t>0.0988</t>
+          <t>0.0718</t>
         </is>
       </c>
       <c r="AT132" t="inlineStr">
         <is>
-          <t>0.2663</t>
+          <t>0.2389</t>
         </is>
       </c>
       <c r="AU132" t="inlineStr">
         <is>
-          <t>69.94</t>
+          <t>69.86</t>
         </is>
       </c>
       <c r="AV132" t="inlineStr">
         <is>
-          <t>7.57</t>
+          <t>7.12</t>
         </is>
       </c>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>34.76</t>
+          <t>40.05</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>26.72</t>
+          <t>22.48</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="AZ132" t="inlineStr">
         <is>
-          <t>0.1042</t>
-        </is>
-      </c>
-      <c r="BA132" t="inlineStr">
-        <is>
-          <t>7.16</t>
-        </is>
-      </c>
-      <c r="BB132" t="inlineStr">
-        <is>
-          <t>37.97</t>
-        </is>
-      </c>
-      <c r="BC132" t="inlineStr">
-        <is>
-          <t>89.22</t>
-        </is>
-      </c>
-      <c r="BD132" t="inlineStr">
-        <is>
-          <t>0.3779</t>
-        </is>
-      </c>
-      <c r="BE132" t="inlineStr">
-        <is>
-          <t>0.1532</t>
-        </is>
-      </c>
-      <c r="BF132" t="inlineStr">
-        <is>
-          <t>26.93</t>
-        </is>
-      </c>
+          <t>0.0473</t>
+        </is>
+      </c>
+      <c r="BA132" t="inlineStr"/>
+      <c r="BB132" t="inlineStr"/>
+      <c r="BC132" t="inlineStr"/>
+      <c r="BD132" t="inlineStr"/>
+      <c r="BE132" t="inlineStr"/>
+      <c r="BF132" t="inlineStr"/>
       <c r="BG132" t="inlineStr"/>
       <c r="BH132" t="inlineStr"/>
       <c r="BI132" t="inlineStr">
         <is>
-          <t>American Family Field</t>
+          <t>Globe Life Field</t>
         </is>
       </c>
       <c r="BJ132" t="inlineStr"/>
@@ -36279,27 +36243,27 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>683766</t>
+          <t>691373</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Christian Koss</t>
+          <t>Jhostynxon Garcia</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>2026-08-04T00:05:00Z</t>
+          <t>2026-08-03T23:40:00Z</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
@@ -36309,14 +36273,26 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="I133" t="inlineStr"/>
-      <c r="J133" t="inlineStr"/>
-      <c r="K133" t="inlineStr"/>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>Brandon Sproat</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>687075</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L133" t="n">
-        <v>30.1</v>
+        <v>27.8</v>
       </c>
       <c r="M133" t="inlineStr">
         <is>
@@ -36334,22 +36310,22 @@
         </is>
       </c>
       <c r="P133" t="n">
-        <v>5.4</v>
+        <v>13.4</v>
       </c>
       <c r="Q133" t="n">
-        <v>41.2</v>
+        <v>37.8</v>
       </c>
       <c r="R133" t="n">
         <v>27.6</v>
       </c>
       <c r="S133" t="n">
-        <v>59.8</v>
+        <v>40.2</v>
       </c>
       <c r="T133" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="U133" t="n">
-        <v>10.6</v>
+        <v>0</v>
       </c>
       <c r="V133" t="inlineStr">
         <is>
@@ -36363,7 +36339,7 @@
       </c>
       <c r="X133" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y133" t="inlineStr">
@@ -36388,7 +36364,7 @@
       </c>
       <c r="AC133" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD133" t="inlineStr"/>
@@ -36405,12 +36381,12 @@
       </c>
       <c r="AH133" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI133" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AJ133" t="inlineStr">
@@ -36420,12 +36396,12 @@
       </c>
       <c r="AK133" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/21, 0 HR</t>
+          <t>Last 7 games: 2/17, 0 HR</t>
         </is>
       </c>
       <c r="AL133" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.3% barrel, 11.9 HR allowed</t>
         </is>
       </c>
       <c r="AM133" t="inlineStr">
@@ -36435,80 +36411,104 @@
       </c>
       <c r="AN133" t="inlineStr">
         <is>
-          <t>3.83</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="AO133" t="inlineStr">
         <is>
-          <t>26.53</t>
+          <t>37.61</t>
         </is>
       </c>
       <c r="AP133" t="inlineStr">
         <is>
-          <t>84.66</t>
+          <t>86.41</t>
         </is>
       </c>
       <c r="AQ133" t="inlineStr">
         <is>
-          <t>96.0366</t>
+          <t>97.4476</t>
         </is>
       </c>
       <c r="AR133" t="inlineStr">
         <is>
-          <t>0.2732</t>
+          <t>0.2955</t>
         </is>
       </c>
       <c r="AS133" t="inlineStr">
         <is>
-          <t>0.0718</t>
+          <t>0.0753</t>
         </is>
       </c>
       <c r="AT133" t="inlineStr">
         <is>
-          <t>0.2389</t>
+          <t>0.2698</t>
         </is>
       </c>
       <c r="AU133" t="inlineStr">
         <is>
-          <t>69.86</t>
+          <t>74.72</t>
         </is>
       </c>
       <c r="AV133" t="inlineStr">
         <is>
-          <t>7.12</t>
+          <t>46.99</t>
         </is>
       </c>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>40.05</t>
+          <t>39.85</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>22.48</t>
+          <t>11.27</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ133" t="inlineStr">
         <is>
-          <t>0.0473</t>
-        </is>
-      </c>
-      <c r="BA133" t="inlineStr"/>
-      <c r="BB133" t="inlineStr"/>
-      <c r="BC133" t="inlineStr"/>
-      <c r="BD133" t="inlineStr"/>
-      <c r="BE133" t="inlineStr"/>
-      <c r="BF133" t="inlineStr"/>
+          <t>0.0583</t>
+        </is>
+      </c>
+      <c r="BA133" t="inlineStr">
+        <is>
+          <t>7.32</t>
+        </is>
+      </c>
+      <c r="BB133" t="inlineStr">
+        <is>
+          <t>41.61</t>
+        </is>
+      </c>
+      <c r="BC133" t="inlineStr">
+        <is>
+          <t>89.3</t>
+        </is>
+      </c>
+      <c r="BD133" t="inlineStr">
+        <is>
+          <t>0.3962</t>
+        </is>
+      </c>
+      <c r="BE133" t="inlineStr">
+        <is>
+          <t>0.1472</t>
+        </is>
+      </c>
+      <c r="BF133" t="inlineStr">
+        <is>
+          <t>22.9</t>
+        </is>
+      </c>
       <c r="BG133" t="inlineStr"/>
       <c r="BH133" t="inlineStr"/>
       <c r="BI133" t="inlineStr">
         <is>
-          <t>Globe Life Field</t>
+          <t>American Family Field</t>
         </is>
       </c>
       <c r="BJ133" t="inlineStr"/>
@@ -36519,27 +36519,27 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>691373</t>
+          <t>702222</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Jhostynxon Garcia</t>
+          <t>Justin Crawford</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>2026-08-03T23:40:00Z</t>
+          <t>2026-08-03T22:40:00Z</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
@@ -36554,21 +36554,21 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>Brandon Sproat</t>
+          <t>Andrew Alvarez</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>687075</t>
+          <t>674841</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L134" t="n">
-        <v>27.8</v>
+        <v>25.3</v>
       </c>
       <c r="M134" t="inlineStr">
         <is>
@@ -36586,13 +36586,13 @@
         </is>
       </c>
       <c r="P134" t="n">
-        <v>13.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Q134" t="n">
-        <v>37.8</v>
+        <v>23</v>
       </c>
       <c r="R134" t="n">
-        <v>27.6</v>
+        <v>34.3</v>
       </c>
       <c r="S134" t="n">
         <v>40.2</v>
@@ -36601,7 +36601,7 @@
         <v>50</v>
       </c>
       <c r="U134" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="V134" t="inlineStr">
         <is>
@@ -36640,7 +36640,7 @@
       </c>
       <c r="AC134" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD134" t="inlineStr"/>
@@ -36657,12 +36657,12 @@
       </c>
       <c r="AH134" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI134" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ134" t="inlineStr">
@@ -36672,12 +36672,12 @@
       </c>
       <c r="AK134" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/17, 0 HR</t>
+          <t>Contact streak: 8/24 over last 7 games</t>
         </is>
       </c>
       <c r="AL134" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.3% barrel, 11.9 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 4.8% barrel, 1.7 HR allowed</t>
         </is>
       </c>
       <c r="AM134" t="inlineStr">
@@ -36687,104 +36687,104 @@
       </c>
       <c r="AN134" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="AO134" t="inlineStr">
         <is>
-          <t>37.61</t>
+          <t>32.9</t>
         </is>
       </c>
       <c r="AP134" t="inlineStr">
         <is>
-          <t>86.41</t>
+          <t>86.6</t>
         </is>
       </c>
       <c r="AQ134" t="inlineStr">
         <is>
-          <t>97.4476</t>
+          <t>97.595</t>
         </is>
       </c>
       <c r="AR134" t="inlineStr">
         <is>
-          <t>0.2955</t>
+          <t>0.317</t>
         </is>
       </c>
       <c r="AS134" t="inlineStr">
         <is>
-          <t>0.0753</t>
+          <t>0.061</t>
         </is>
       </c>
       <c r="AT134" t="inlineStr">
         <is>
-          <t>0.2698</t>
+          <t>0.278</t>
         </is>
       </c>
       <c r="AU134" t="inlineStr">
         <is>
-          <t>74.72</t>
+          <t>68.9</t>
         </is>
       </c>
       <c r="AV134" t="inlineStr">
         <is>
-          <t>46.99</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>39.85</t>
+          <t>27.6</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>11.27</t>
+          <t>16.5</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AZ134" t="inlineStr">
         <is>
-          <t>0.0583</t>
+          <t>0.082</t>
         </is>
       </c>
       <c r="BA134" t="inlineStr">
         <is>
-          <t>7.32</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="BB134" t="inlineStr">
         <is>
-          <t>41.61</t>
+          <t>41.92</t>
         </is>
       </c>
       <c r="BC134" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>89.32</t>
         </is>
       </c>
       <c r="BD134" t="inlineStr">
         <is>
-          <t>0.3962</t>
+          <t>0.3507</t>
         </is>
       </c>
       <c r="BE134" t="inlineStr">
         <is>
-          <t>0.1472</t>
+          <t>0.1053</t>
         </is>
       </c>
       <c r="BF134" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>16.01</t>
         </is>
       </c>
       <c r="BG134" t="inlineStr"/>
       <c r="BH134" t="inlineStr"/>
       <c r="BI134" t="inlineStr">
         <is>
-          <t>American Family Field</t>
+          <t>Citizens Bank Park</t>
         </is>
       </c>
       <c r="BJ134" t="inlineStr"/>
@@ -36795,27 +36795,27 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>702222</t>
+          <t>670032</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Justin Crawford</t>
+          <t>Nicky Lopez</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>2026-08-03T22:40:00Z</t>
+          <t>2026-08-04T00:05:00Z</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
@@ -36830,21 +36830,21 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>Andrew Alvarez</t>
+          <t>Logan Webb</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>674841</t>
+          <t>657277</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L135" t="n">
-        <v>25.3</v>
+        <v>25.1</v>
       </c>
       <c r="M135" t="inlineStr">
         <is>
@@ -36858,26 +36858,26 @@
       </c>
       <c r="O135" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P135" t="n">
-        <v>8.800000000000001</v>
+        <v>2.5</v>
       </c>
       <c r="Q135" t="n">
-        <v>23</v>
+        <v>30.6</v>
       </c>
       <c r="R135" t="n">
-        <v>34.3</v>
+        <v>27.6</v>
       </c>
       <c r="S135" t="n">
         <v>40.2</v>
       </c>
       <c r="T135" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U135" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="V135" t="inlineStr">
         <is>
@@ -36916,7 +36916,7 @@
       </c>
       <c r="AC135" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD135" t="inlineStr"/>
@@ -36933,12 +36933,12 @@
       </c>
       <c r="AH135" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AI135" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ135" t="inlineStr">
@@ -36948,12 +36948,12 @@
       </c>
       <c r="AK135" t="inlineStr">
         <is>
-          <t>Contact streak: 8/24 over last 7 games</t>
+          <t>Last 7 games: 1/19, 0 HR</t>
         </is>
       </c>
       <c r="AL135" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 4.8% barrel, 1.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.4% barrel, 10.5 HR allowed</t>
         </is>
       </c>
       <c r="AM135" t="inlineStr">
@@ -36963,383 +36963,107 @@
       </c>
       <c r="AN135" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AO135" t="inlineStr">
         <is>
-          <t>32.9</t>
+          <t>28.17</t>
         </is>
       </c>
       <c r="AP135" t="inlineStr">
         <is>
-          <t>86.6</t>
+          <t>84.66</t>
         </is>
       </c>
       <c r="AQ135" t="inlineStr">
         <is>
-          <t>97.595</t>
+          <t>95.4793</t>
         </is>
       </c>
       <c r="AR135" t="inlineStr">
         <is>
-          <t>0.317</t>
+          <t>0.2648</t>
         </is>
       </c>
       <c r="AS135" t="inlineStr">
         <is>
-          <t>0.061</t>
+          <t>0.0398</t>
         </is>
       </c>
       <c r="AT135" t="inlineStr">
         <is>
-          <t>0.278</t>
+          <t>0.2568</t>
         </is>
       </c>
       <c r="AU135" t="inlineStr">
         <is>
-          <t>68.9</t>
+          <t>66.58</t>
         </is>
       </c>
       <c r="AV135" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>27.6</t>
+          <t>34.08</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>16.5</t>
+          <t>11.3</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="AZ135" t="inlineStr">
         <is>
-          <t>0.082</t>
+          <t>0.0259</t>
         </is>
       </c>
       <c r="BA135" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>6.41</t>
         </is>
       </c>
       <c r="BB135" t="inlineStr">
         <is>
-          <t>41.92</t>
+          <t>39.57</t>
         </is>
       </c>
       <c r="BC135" t="inlineStr">
         <is>
-          <t>89.32</t>
+          <t>88.79</t>
         </is>
       </c>
       <c r="BD135" t="inlineStr">
         <is>
-          <t>0.3507</t>
+          <t>0.3826</t>
         </is>
       </c>
       <c r="BE135" t="inlineStr">
         <is>
-          <t>0.1053</t>
+          <t>0.1289</t>
         </is>
       </c>
       <c r="BF135" t="inlineStr">
         <is>
-          <t>16.01</t>
+          <t>18.65</t>
         </is>
       </c>
       <c r="BG135" t="inlineStr"/>
       <c r="BH135" t="inlineStr"/>
       <c r="BI135" t="inlineStr">
         <is>
-          <t>Citizens Bank Park</t>
+          <t>Globe Life Field</t>
         </is>
       </c>
       <c r="BJ135" t="inlineStr"/>
-    </row>
-    <row r="136">
-      <c r="A136" t="n">
-        <v>135</v>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>670032</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>Nicky Lopez</t>
-        </is>
-      </c>
-      <c r="D136" t="inlineStr">
-        <is>
-          <t>TEX</t>
-        </is>
-      </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>SF</t>
-        </is>
-      </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>2026-08-04T00:05:00Z</t>
-        </is>
-      </c>
-      <c r="G136" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="H136" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr">
-        <is>
-          <t>Logan Webb</t>
-        </is>
-      </c>
-      <c r="J136" t="inlineStr">
-        <is>
-          <t>657277</t>
-        </is>
-      </c>
-      <c r="K136" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="L136" t="n">
-        <v>25.1</v>
-      </c>
-      <c r="M136" t="inlineStr">
-        <is>
-          <t>Longshot</t>
-        </is>
-      </c>
-      <c r="N136" t="inlineStr">
-        <is>
-          <t>Watch List</t>
-        </is>
-      </c>
-      <c r="O136" t="inlineStr">
-        <is>
-          <t>Projected Lineup, Platoon Edge</t>
-        </is>
-      </c>
-      <c r="P136" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q136" t="n">
-        <v>30.6</v>
-      </c>
-      <c r="R136" t="n">
-        <v>27.6</v>
-      </c>
-      <c r="S136" t="n">
-        <v>40.2</v>
-      </c>
-      <c r="T136" t="n">
-        <v>80</v>
-      </c>
-      <c r="U136" t="n">
-        <v>0</v>
-      </c>
-      <c r="V136" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W136" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X136" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y136" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z136" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AA136" t="inlineStr">
-        <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB136" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
-      <c r="AC136" t="inlineStr">
-        <is>
-          <t>H:2026/2025 P:2026/2025</t>
-        </is>
-      </c>
-      <c r="AD136" t="inlineStr"/>
-      <c r="AE136" t="inlineStr"/>
-      <c r="AF136" t="inlineStr">
-        <is>
-          <t>Direct BvP not yet weighted; 2026/2025 Statcast baseline active</t>
-        </is>
-      </c>
-      <c r="AG136" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AH136" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AI136" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="AJ136" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK136" t="inlineStr">
-        <is>
-          <t>Last 7 games: 1/19, 0 HR</t>
-        </is>
-      </c>
-      <c r="AL136" t="inlineStr">
-        <is>
-          <t>platoon edge; pitcher baseline 6.4% barrel, 10.5 HR allowed</t>
-        </is>
-      </c>
-      <c r="AM136" t="inlineStr">
-        <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
-        </is>
-      </c>
-      <c r="AN136" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AO136" t="inlineStr">
-        <is>
-          <t>28.17</t>
-        </is>
-      </c>
-      <c r="AP136" t="inlineStr">
-        <is>
-          <t>84.66</t>
-        </is>
-      </c>
-      <c r="AQ136" t="inlineStr">
-        <is>
-          <t>95.4793</t>
-        </is>
-      </c>
-      <c r="AR136" t="inlineStr">
-        <is>
-          <t>0.2648</t>
-        </is>
-      </c>
-      <c r="AS136" t="inlineStr">
-        <is>
-          <t>0.0398</t>
-        </is>
-      </c>
-      <c r="AT136" t="inlineStr">
-        <is>
-          <t>0.2568</t>
-        </is>
-      </c>
-      <c r="AU136" t="inlineStr">
-        <is>
-          <t>66.58</t>
-        </is>
-      </c>
-      <c r="AV136" t="inlineStr">
-        <is>
-          <t>0.75</t>
-        </is>
-      </c>
-      <c r="AW136" t="inlineStr">
-        <is>
-          <t>34.08</t>
-        </is>
-      </c>
-      <c r="AX136" t="inlineStr">
-        <is>
-          <t>11.3</t>
-        </is>
-      </c>
-      <c r="AY136" t="inlineStr">
-        <is>
-          <t>0.7</t>
-        </is>
-      </c>
-      <c r="AZ136" t="inlineStr">
-        <is>
-          <t>0.0259</t>
-        </is>
-      </c>
-      <c r="BA136" t="inlineStr">
-        <is>
-          <t>6.41</t>
-        </is>
-      </c>
-      <c r="BB136" t="inlineStr">
-        <is>
-          <t>39.57</t>
-        </is>
-      </c>
-      <c r="BC136" t="inlineStr">
-        <is>
-          <t>88.79</t>
-        </is>
-      </c>
-      <c r="BD136" t="inlineStr">
-        <is>
-          <t>0.3826</t>
-        </is>
-      </c>
-      <c r="BE136" t="inlineStr">
-        <is>
-          <t>0.1289</t>
-        </is>
-      </c>
-      <c r="BF136" t="inlineStr">
-        <is>
-          <t>18.65</t>
-        </is>
-      </c>
-      <c r="BG136" t="inlineStr"/>
-      <c r="BH136" t="inlineStr"/>
-      <c r="BI136" t="inlineStr">
-        <is>
-          <t>Globe Life Field</t>
-        </is>
-      </c>
-      <c r="BJ136" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
